--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A756FBA-91FE-4CE9-BBF0-7D37C7AA8E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB58B22-A593-4C09-9A55-F613C1A69021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
   <si>
     <t>كد</t>
   </si>
@@ -864,9 +864,6 @@
     <t>2200038</t>
   </si>
   <si>
-    <t>2500006</t>
-  </si>
-  <si>
     <t>2200021</t>
   </si>
   <si>
@@ -1605,9 +1602,6 @@
     <t>برگر ويژه سكه طلا</t>
   </si>
   <si>
-    <t>برگر ويژه با فيله سوخاري</t>
-  </si>
-  <si>
     <t>برگر ويژه با پنير مخصوص</t>
   </si>
   <si>
@@ -1704,13 +1698,22 @@
     <t>ال اسپشيال فلفل فرنگي</t>
   </si>
   <si>
-    <t>اسكاچ</t>
-  </si>
-  <si>
     <t>ادويه سيب</t>
   </si>
   <si>
     <t>پيتزا مرغ  و قارچ</t>
+  </si>
+  <si>
+    <t>ويژه با فيله سوخاري</t>
+  </si>
+  <si>
+    <t>بوفالو وینگز</t>
+  </si>
+  <si>
+    <t>خوراک فیله سوخاری دو تکه</t>
+  </si>
+  <si>
+    <t>لیوان</t>
   </si>
 </sst>
 </file>
@@ -2047,10 +2050,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B281"/>
+  <dimension ref="A1:B283"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2059,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2067,7 +2070,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2075,7 +2078,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2083,7 +2086,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2091,7 +2094,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2099,7 +2102,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2107,7 +2110,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2115,7 +2118,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2123,7 +2126,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2131,7 +2134,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2139,7 +2142,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2147,7 +2150,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2155,7 +2158,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2163,7 +2166,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2171,7 +2174,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2179,7 +2182,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2187,7 +2190,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2195,7 +2198,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2203,7 +2206,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2211,7 +2214,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2219,7 +2222,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2227,7 +2230,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2235,7 +2238,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2243,7 +2246,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2251,7 +2254,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2259,7 +2262,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2267,7 +2270,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2275,7 +2278,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2283,7 +2286,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2291,7 +2294,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2299,7 +2302,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2307,7 +2310,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2315,7 +2318,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2323,7 +2326,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2331,7 +2334,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2339,7 +2342,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2347,7 +2350,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2355,7 +2358,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2363,7 +2366,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2371,7 +2374,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2379,7 +2382,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2387,7 +2390,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2395,7 +2398,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2403,7 +2406,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2411,7 +2414,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2419,7 +2422,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2427,7 +2430,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2435,7 +2438,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2443,7 +2446,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2451,7 +2454,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2459,7 +2462,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2467,7 +2470,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2475,7 +2478,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2483,7 +2486,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2491,7 +2494,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2499,7 +2502,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2507,7 +2510,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2515,7 +2518,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2523,7 +2526,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2531,7 +2534,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2539,7 +2542,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2547,7 +2550,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2555,7 +2558,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2563,7 +2566,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2571,7 +2574,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2579,7 +2582,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2587,7 +2590,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2595,7 +2598,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2603,7 +2606,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2611,7 +2614,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2619,7 +2622,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2627,7 +2630,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2635,7 +2638,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2643,7 +2646,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2651,7 +2654,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2659,7 +2662,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2667,7 +2670,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2675,7 +2678,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2683,7 +2686,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2691,7 +2694,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2699,7 +2702,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2707,7 +2710,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2715,7 +2718,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2723,7 +2726,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2731,7 +2734,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2739,7 +2742,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2747,7 +2750,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2755,7 +2758,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2763,7 +2766,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2771,7 +2774,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2779,7 +2782,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2787,7 +2790,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2795,7 +2798,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2803,7 +2806,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -2811,7 +2814,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -2819,7 +2822,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2827,7 +2830,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -2835,7 +2838,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -2843,7 +2846,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -2851,7 +2854,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2859,7 +2862,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -2867,7 +2870,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -2875,7 +2878,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -2883,7 +2886,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -2891,7 +2894,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -2899,7 +2902,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -2907,7 +2910,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -2915,7 +2918,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -2923,7 +2926,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -2931,7 +2934,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2939,7 +2942,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2947,7 +2950,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -2955,7 +2958,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -2963,7 +2966,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -2971,7 +2974,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2979,7 +2982,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -2987,7 +2990,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -2995,7 +2998,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -3003,7 +3006,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -3011,7 +3014,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -3019,7 +3022,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -3027,7 +3030,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -3035,7 +3038,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -3043,7 +3046,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -3051,7 +3054,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -3059,7 +3062,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -3067,7 +3070,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -3075,7 +3078,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -3083,7 +3086,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -3091,7 +3094,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -3099,7 +3102,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -3107,7 +3110,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -3115,7 +3118,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -3123,7 +3126,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -3131,7 +3134,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -3139,7 +3142,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -3147,7 +3150,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -3155,7 +3158,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -3163,7 +3166,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -3171,7 +3174,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -3179,7 +3182,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -3187,7 +3190,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -3195,7 +3198,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -3203,7 +3206,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -3211,7 +3214,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -3219,7 +3222,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -3227,7 +3230,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -3235,7 +3238,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -3243,7 +3246,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3251,7 +3254,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3259,7 +3262,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -3267,7 +3270,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -3275,7 +3278,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -3283,7 +3286,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -3291,7 +3294,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -3299,7 +3302,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -3307,7 +3310,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -3315,7 +3318,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -3323,7 +3326,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -3331,7 +3334,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -3339,7 +3342,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -3347,7 +3350,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -3355,7 +3358,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -3363,7 +3366,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -3371,7 +3374,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -3379,7 +3382,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -3387,7 +3390,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -3395,7 +3398,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -3403,7 +3406,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -3411,7 +3414,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -3419,7 +3422,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -3427,7 +3430,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -3435,7 +3438,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3443,7 +3446,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -3451,7 +3454,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -3459,7 +3462,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -3467,7 +3470,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3475,7 +3478,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -3483,7 +3486,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3491,7 +3494,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -3499,7 +3502,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -3507,7 +3510,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3515,7 +3518,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -3523,7 +3526,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -3531,7 +3534,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -3539,7 +3542,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -3547,7 +3550,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -3555,7 +3558,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -3563,7 +3566,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -3571,7 +3574,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -3579,7 +3582,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3587,7 +3590,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3595,7 +3598,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3603,7 +3606,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3611,7 +3614,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3619,7 +3622,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3627,7 +3630,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3635,7 +3638,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3643,7 +3646,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3651,7 +3654,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3659,7 +3662,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3667,7 +3670,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3675,7 +3678,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3683,7 +3686,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3691,7 +3694,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3699,7 +3702,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3707,7 +3710,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3715,7 +3718,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -3723,7 +3726,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3731,7 +3734,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -3739,7 +3742,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -3747,7 +3750,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -3755,7 +3758,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -3763,7 +3766,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -3771,7 +3774,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -3779,7 +3782,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -3787,7 +3790,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -3795,7 +3798,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -3803,7 +3806,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -3811,7 +3814,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -3819,7 +3822,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -3827,7 +3830,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -3835,7 +3838,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -3843,7 +3846,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -3851,7 +3854,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -3859,7 +3862,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -3867,7 +3870,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -3875,7 +3878,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -3883,7 +3886,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -3891,7 +3894,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -3899,7 +3902,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -3907,7 +3910,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -3915,7 +3918,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -3923,7 +3926,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -3931,7 +3934,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -3939,7 +3942,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -3947,7 +3950,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -3955,7 +3958,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -3963,7 +3966,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -3971,7 +3974,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -3979,7 +3982,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -3987,7 +3990,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -3995,7 +3998,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -4003,7 +4006,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -4011,7 +4014,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -4019,7 +4022,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -4027,7 +4030,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>526</v>
+        <v>559</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -4035,7 +4038,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -4043,7 +4046,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -4051,7 +4054,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -4059,7 +4062,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -4067,7 +4070,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -4075,7 +4078,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -4083,7 +4086,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -4091,7 +4094,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -4099,7 +4102,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -4107,7 +4110,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -4115,7 +4118,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -4123,7 +4126,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -4131,7 +4134,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -4139,7 +4142,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -4147,7 +4150,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -4155,7 +4158,7 @@
         <v>262</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -4163,7 +4166,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -4171,7 +4174,7 @@
         <v>264</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
@@ -4179,7 +4182,7 @@
         <v>265</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
@@ -4187,7 +4190,7 @@
         <v>266</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
@@ -4195,7 +4198,7 @@
         <v>267</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -4203,7 +4206,7 @@
         <v>268</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
@@ -4211,7 +4214,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
@@ -4219,7 +4222,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
@@ -4227,7 +4230,7 @@
         <v>271</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
@@ -4235,7 +4238,7 @@
         <v>272</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
@@ -4243,7 +4246,7 @@
         <v>273</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
@@ -4251,7 +4254,7 @@
         <v>274</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
@@ -4259,7 +4262,7 @@
         <v>275</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
@@ -4267,7 +4270,7 @@
         <v>276</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
@@ -4275,7 +4278,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
@@ -4283,23 +4286,39 @@
         <v>278</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" s="2" t="s">
-        <v>279</v>
+      <c r="A280" s="2">
+        <v>2500013</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B281" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>1100057</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>560</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>1100059</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>

--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB58B22-A593-4C09-9A55-F613C1A69021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5B39AE-8947-4C0C-A044-634A0F9F954C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="565">
   <si>
     <t>كد</t>
   </si>
@@ -1714,6 +1714,12 @@
   </si>
   <si>
     <t>لیوان</t>
+  </si>
+  <si>
+    <t>سس هانی بالزامیک</t>
+  </si>
+  <si>
+    <t>سس تکنفره مایونز</t>
   </si>
 </sst>
 </file>
@@ -2050,10 +2056,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B283"/>
+  <dimension ref="A1:B285"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4321,6 +4327,22 @@
         <v>561</v>
       </c>
     </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>1100038</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>2100021</v>
+      </c>
+      <c r="B285" t="s">
+        <v>564</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Desktop\temp\seketala\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A5B39AE-8947-4C0C-A044-634A0F9F954C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA2439C-E691-4D0C-ABC7-FE05FEBB1B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1380" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" calcOnSave="0"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="568">
   <si>
     <t>كد</t>
   </si>
@@ -1720,6 +1720,15 @@
   </si>
   <si>
     <t>سس تکنفره مایونز</t>
+  </si>
+  <si>
+    <t>سس فرانسوي</t>
+  </si>
+  <si>
+    <t>سس خردل</t>
+  </si>
+  <si>
+    <t>سالاد کلم</t>
   </si>
 </sst>
 </file>
@@ -2056,7 +2065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B285"/>
+  <dimension ref="A1:B288"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -4343,6 +4352,30 @@
         <v>564</v>
       </c>
     </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>1100062</v>
+      </c>
+      <c r="B286" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>1100061</v>
+      </c>
+      <c r="B287" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A288">
+        <v>1100060</v>
+      </c>
+      <c r="B288" t="s">
+        <v>567</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Desktop\temp\seketala\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA2439C-E691-4D0C-ABC7-FE05FEBB1B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D4D3D6-1B0E-4CA4-AF82-6262BA7B5F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1380" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="624">
   <si>
     <t>كد</t>
   </si>
@@ -1729,6 +1729,174 @@
   </si>
   <si>
     <t>سالاد کلم</t>
+  </si>
+  <si>
+    <t>1100065</t>
+  </si>
+  <si>
+    <t>1100066</t>
+  </si>
+  <si>
+    <t>آب معدني 300 سي سي</t>
+  </si>
+  <si>
+    <t>1100067</t>
+  </si>
+  <si>
+    <t>خانواده كوكا با ليوان</t>
+  </si>
+  <si>
+    <t>1100068</t>
+  </si>
+  <si>
+    <t>خانواده فانتا با ليوان</t>
+  </si>
+  <si>
+    <t>1100069</t>
+  </si>
+  <si>
+    <t>خانواده اسپرايت با ليوان</t>
+  </si>
+  <si>
+    <t>1100070</t>
+  </si>
+  <si>
+    <t>خانواده ليموناد فانتا با ليوان</t>
+  </si>
+  <si>
+    <t>1100071</t>
+  </si>
+  <si>
+    <t>خانواده مشكي زيرو با ليوان</t>
+  </si>
+  <si>
+    <t>1100072</t>
+  </si>
+  <si>
+    <t>خانواده شاه توت با ليوان</t>
+  </si>
+  <si>
+    <t>1100073</t>
+  </si>
+  <si>
+    <t>قوطي كوكا با ليوان</t>
+  </si>
+  <si>
+    <t>1100074</t>
+  </si>
+  <si>
+    <t>قوطي فانتا با ليوان</t>
+  </si>
+  <si>
+    <t>1100075</t>
+  </si>
+  <si>
+    <t>قوطي زيرو با ليوان</t>
+  </si>
+  <si>
+    <t>1100076</t>
+  </si>
+  <si>
+    <t>قوطي ليموناد خوشگوار با ليوان</t>
+  </si>
+  <si>
+    <t>1100077</t>
+  </si>
+  <si>
+    <t>قوطي اسپرايت با ليوان</t>
+  </si>
+  <si>
+    <t>1100078</t>
+  </si>
+  <si>
+    <t>هي دي ليمو با ليوان</t>
+  </si>
+  <si>
+    <t>1100079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هي دي هلو با ليوان </t>
+  </si>
+  <si>
+    <t>1100080</t>
+  </si>
+  <si>
+    <t>هي دي استوايي با ليوان</t>
+  </si>
+  <si>
+    <t>1100081</t>
+  </si>
+  <si>
+    <t>هي دي كلاسيك با ليوان</t>
+  </si>
+  <si>
+    <t>1100082</t>
+  </si>
+  <si>
+    <t>هافنبرگ كاكتوس با ليوان</t>
+  </si>
+  <si>
+    <t>1100083</t>
+  </si>
+  <si>
+    <t>دوغ خوشگوار با ليوان</t>
+  </si>
+  <si>
+    <t>هي دي كلاسيك</t>
+  </si>
+  <si>
+    <t>1100056</t>
+  </si>
+  <si>
+    <t>كالاي تست ارزش افزوده</t>
+  </si>
+  <si>
+    <t>1100057</t>
+  </si>
+  <si>
+    <t>بوفالو وينگز فروش</t>
+  </si>
+  <si>
+    <t>1100058</t>
+  </si>
+  <si>
+    <t>سالاد سزار مرغ فروش</t>
+  </si>
+  <si>
+    <t>1100059</t>
+  </si>
+  <si>
+    <t>خوراك فيله سوخاري دو تكه</t>
+  </si>
+  <si>
+    <t>1100060</t>
+  </si>
+  <si>
+    <t>سالاد كلم تكي</t>
+  </si>
+  <si>
+    <t>1100061</t>
+  </si>
+  <si>
+    <t>سس خردل تكي</t>
+  </si>
+  <si>
+    <t>1100062</t>
+  </si>
+  <si>
+    <t>سس فرانسوي تكي</t>
+  </si>
+  <si>
+    <t>1100063</t>
+  </si>
+  <si>
+    <t>خانواده ليمويي</t>
+  </si>
+  <si>
+    <t>1100064</t>
+  </si>
+  <si>
+    <t>خانواده شاتوت</t>
   </si>
 </sst>
 </file>
@@ -1754,7 +1922,7 @@
       <name val="Tahoma"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1764,6 +1932,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFECF4FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F1FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1780,11 +1954,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2065,7 +2242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:R332"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -4376,6 +4553,964 @@
         <v>567</v>
       </c>
     </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A289" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B289" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C289" s="2"/>
+      <c r="F289" s="2"/>
+      <c r="G289" s="2"/>
+      <c r="H289" s="2"/>
+      <c r="I289" s="2"/>
+      <c r="J289" s="2"/>
+      <c r="K289" s="2"/>
+      <c r="L289" s="5"/>
+      <c r="M289" s="2"/>
+      <c r="N289" s="5"/>
+      <c r="O289" s="2"/>
+      <c r="P289" s="2"/>
+      <c r="Q289" s="2"/>
+      <c r="R289" s="2"/>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C290" s="3"/>
+      <c r="F290" s="3"/>
+      <c r="G290" s="3"/>
+      <c r="H290" s="3"/>
+      <c r="I290" s="3"/>
+      <c r="J290" s="3"/>
+      <c r="K290" s="3"/>
+      <c r="L290" s="6"/>
+      <c r="M290" s="3"/>
+      <c r="N290" s="6"/>
+      <c r="O290" s="3"/>
+      <c r="P290" s="3"/>
+      <c r="Q290" s="3"/>
+      <c r="R290" s="3"/>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A291" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C291" s="3"/>
+      <c r="F291" s="3"/>
+      <c r="G291" s="3"/>
+      <c r="H291" s="3"/>
+      <c r="I291" s="3"/>
+      <c r="J291" s="3"/>
+      <c r="K291" s="3"/>
+      <c r="L291" s="6"/>
+      <c r="M291" s="3"/>
+      <c r="N291" s="6"/>
+      <c r="O291" s="3"/>
+      <c r="P291" s="3"/>
+      <c r="Q291" s="3"/>
+      <c r="R291" s="3"/>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C292" s="2"/>
+      <c r="F292" s="2"/>
+      <c r="G292" s="2"/>
+      <c r="H292" s="2"/>
+      <c r="I292" s="2"/>
+      <c r="J292" s="2"/>
+      <c r="K292" s="2"/>
+      <c r="L292" s="5"/>
+      <c r="M292" s="2"/>
+      <c r="N292" s="5"/>
+      <c r="O292" s="2"/>
+      <c r="P292" s="2"/>
+      <c r="Q292" s="2"/>
+      <c r="R292" s="2"/>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A293" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C293" s="3"/>
+      <c r="F293" s="3"/>
+      <c r="G293" s="3"/>
+      <c r="H293" s="3"/>
+      <c r="I293" s="3"/>
+      <c r="J293" s="3"/>
+      <c r="K293" s="3"/>
+      <c r="L293" s="6"/>
+      <c r="M293" s="3"/>
+      <c r="N293" s="6"/>
+      <c r="O293" s="3"/>
+      <c r="P293" s="3"/>
+      <c r="Q293" s="3"/>
+      <c r="R293" s="3"/>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C294" s="2"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="2"/>
+      <c r="H294" s="2"/>
+      <c r="I294" s="2"/>
+      <c r="J294" s="2"/>
+      <c r="K294" s="2"/>
+      <c r="L294" s="5"/>
+      <c r="M294" s="2"/>
+      <c r="N294" s="5"/>
+      <c r="O294" s="2"/>
+      <c r="P294" s="2"/>
+      <c r="Q294" s="2"/>
+      <c r="R294" s="2"/>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A295" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C295" s="3"/>
+      <c r="F295" s="3"/>
+      <c r="G295" s="3"/>
+      <c r="H295" s="3"/>
+      <c r="I295" s="3"/>
+      <c r="J295" s="3"/>
+      <c r="K295" s="3"/>
+      <c r="L295" s="6"/>
+      <c r="M295" s="3"/>
+      <c r="N295" s="6"/>
+      <c r="O295" s="3"/>
+      <c r="P295" s="3"/>
+      <c r="Q295" s="3"/>
+      <c r="R295" s="3"/>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C296" s="2"/>
+      <c r="F296" s="2"/>
+      <c r="G296" s="2"/>
+      <c r="H296" s="2"/>
+      <c r="I296" s="2"/>
+      <c r="J296" s="2"/>
+      <c r="K296" s="2"/>
+      <c r="L296" s="5"/>
+      <c r="M296" s="2"/>
+      <c r="N296" s="5"/>
+      <c r="O296" s="2"/>
+      <c r="P296" s="2"/>
+      <c r="Q296" s="2"/>
+      <c r="R296" s="2"/>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A297" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C297" s="3"/>
+      <c r="F297" s="3"/>
+      <c r="G297" s="3"/>
+      <c r="H297" s="3"/>
+      <c r="I297" s="3"/>
+      <c r="J297" s="3"/>
+      <c r="K297" s="3"/>
+      <c r="L297" s="6"/>
+      <c r="M297" s="3"/>
+      <c r="N297" s="6"/>
+      <c r="O297" s="3"/>
+      <c r="P297" s="3"/>
+      <c r="Q297" s="3"/>
+      <c r="R297" s="3"/>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C298" s="2"/>
+      <c r="F298" s="2"/>
+      <c r="G298" s="2"/>
+      <c r="H298" s="2"/>
+      <c r="I298" s="2"/>
+      <c r="J298" s="2"/>
+      <c r="K298" s="2"/>
+      <c r="L298" s="5"/>
+      <c r="M298" s="2"/>
+      <c r="N298" s="5"/>
+      <c r="O298" s="2"/>
+      <c r="P298" s="2"/>
+      <c r="Q298" s="2"/>
+      <c r="R298" s="2"/>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A299" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C299" s="3"/>
+      <c r="F299" s="3"/>
+      <c r="G299" s="3"/>
+      <c r="H299" s="3"/>
+      <c r="I299" s="3"/>
+      <c r="J299" s="3"/>
+      <c r="K299" s="3"/>
+      <c r="L299" s="6"/>
+      <c r="M299" s="3"/>
+      <c r="N299" s="6"/>
+      <c r="O299" s="3"/>
+      <c r="P299" s="3"/>
+      <c r="Q299" s="3"/>
+      <c r="R299" s="3"/>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
+      <c r="H300" s="2"/>
+      <c r="I300" s="2"/>
+      <c r="J300" s="2"/>
+      <c r="K300" s="2"/>
+      <c r="L300" s="5"/>
+      <c r="M300" s="2"/>
+      <c r="N300" s="5"/>
+      <c r="O300" s="2"/>
+      <c r="P300" s="2"/>
+      <c r="Q300" s="2"/>
+      <c r="R300" s="2"/>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A301" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C301" s="3"/>
+      <c r="F301" s="3"/>
+      <c r="G301" s="3"/>
+      <c r="H301" s="3"/>
+      <c r="I301" s="3"/>
+      <c r="J301" s="3"/>
+      <c r="K301" s="3"/>
+      <c r="L301" s="6"/>
+      <c r="M301" s="3"/>
+      <c r="N301" s="6"/>
+      <c r="O301" s="3"/>
+      <c r="P301" s="3"/>
+      <c r="Q301" s="3"/>
+      <c r="R301" s="3"/>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C302" s="2"/>
+      <c r="F302" s="2"/>
+      <c r="G302" s="2"/>
+      <c r="H302" s="2"/>
+      <c r="I302" s="2"/>
+      <c r="J302" s="2"/>
+      <c r="K302" s="2"/>
+      <c r="L302" s="5"/>
+      <c r="M302" s="2"/>
+      <c r="N302" s="5"/>
+      <c r="O302" s="2"/>
+      <c r="P302" s="2"/>
+      <c r="Q302" s="2"/>
+      <c r="R302" s="2"/>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A303" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="C303" s="3"/>
+      <c r="F303" s="3"/>
+      <c r="G303" s="3"/>
+      <c r="H303" s="3"/>
+      <c r="I303" s="3"/>
+      <c r="J303" s="3"/>
+      <c r="K303" s="3"/>
+      <c r="L303" s="6"/>
+      <c r="M303" s="3"/>
+      <c r="N303" s="6"/>
+      <c r="O303" s="3"/>
+      <c r="P303" s="3"/>
+      <c r="Q303" s="3"/>
+      <c r="R303" s="3"/>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C304" s="2"/>
+      <c r="F304" s="2"/>
+      <c r="G304" s="2"/>
+      <c r="H304" s="2"/>
+      <c r="I304" s="2"/>
+      <c r="J304" s="2"/>
+      <c r="K304" s="2"/>
+      <c r="L304" s="5"/>
+      <c r="M304" s="2"/>
+      <c r="N304" s="5"/>
+      <c r="O304" s="2"/>
+      <c r="P304" s="2"/>
+      <c r="Q304" s="2"/>
+      <c r="R304" s="2"/>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A305" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="C305" s="3"/>
+      <c r="F305" s="3"/>
+      <c r="G305" s="3"/>
+      <c r="H305" s="3"/>
+      <c r="I305" s="3"/>
+      <c r="J305" s="3"/>
+      <c r="K305" s="3"/>
+      <c r="L305" s="6"/>
+      <c r="M305" s="3"/>
+      <c r="N305" s="6"/>
+      <c r="O305" s="3"/>
+      <c r="P305" s="3"/>
+      <c r="Q305" s="3"/>
+      <c r="R305" s="3"/>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C306" s="2"/>
+      <c r="F306" s="2"/>
+      <c r="G306" s="2"/>
+      <c r="H306" s="2"/>
+      <c r="I306" s="2"/>
+      <c r="J306" s="2"/>
+      <c r="K306" s="2"/>
+      <c r="L306" s="5"/>
+      <c r="M306" s="2"/>
+      <c r="N306" s="5"/>
+      <c r="O306" s="2"/>
+      <c r="P306" s="2"/>
+      <c r="Q306" s="2"/>
+      <c r="R306" s="2"/>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A307" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C307" s="3"/>
+      <c r="F307" s="3"/>
+      <c r="G307" s="3"/>
+      <c r="H307" s="3"/>
+      <c r="I307" s="3"/>
+      <c r="J307" s="3"/>
+      <c r="K307" s="3"/>
+      <c r="L307" s="6"/>
+      <c r="M307" s="3"/>
+      <c r="N307" s="6"/>
+      <c r="O307" s="3"/>
+      <c r="P307" s="3"/>
+      <c r="Q307" s="3"/>
+      <c r="R307" s="3"/>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A308" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C308" s="2"/>
+      <c r="F308" s="2"/>
+      <c r="G308" s="2"/>
+      <c r="H308" s="2"/>
+      <c r="I308" s="2"/>
+      <c r="J308" s="2"/>
+      <c r="K308" s="2"/>
+      <c r="L308" s="5"/>
+      <c r="M308" s="2"/>
+      <c r="N308" s="5"/>
+      <c r="O308" s="2"/>
+      <c r="P308" s="2"/>
+      <c r="Q308" s="2"/>
+      <c r="R308" s="2"/>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A309" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="C309" s="3"/>
+      <c r="F309" s="3"/>
+      <c r="G309" s="3"/>
+      <c r="H309" s="3"/>
+      <c r="I309" s="3"/>
+      <c r="J309" s="3"/>
+      <c r="K309" s="3"/>
+      <c r="L309" s="6"/>
+      <c r="M309" s="3"/>
+      <c r="N309" s="6"/>
+      <c r="O309" s="3"/>
+      <c r="P309" s="3"/>
+      <c r="Q309" s="3"/>
+      <c r="R309" s="3"/>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A310" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C310" s="2"/>
+      <c r="F310" s="2"/>
+      <c r="G310" s="2"/>
+      <c r="H310" s="2"/>
+      <c r="I310" s="2"/>
+      <c r="J310" s="2"/>
+      <c r="K310" s="2"/>
+      <c r="L310" s="5"/>
+      <c r="M310" s="2"/>
+      <c r="N310" s="5"/>
+      <c r="O310" s="2"/>
+      <c r="P310" s="2"/>
+      <c r="Q310" s="2"/>
+      <c r="R310" s="2"/>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A311" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="C311" s="3"/>
+      <c r="F311" s="3"/>
+      <c r="G311" s="3"/>
+      <c r="H311" s="3"/>
+      <c r="I311" s="3"/>
+      <c r="J311" s="3"/>
+      <c r="K311" s="3"/>
+      <c r="L311" s="6"/>
+      <c r="M311" s="3"/>
+      <c r="N311" s="6"/>
+      <c r="O311" s="3"/>
+      <c r="P311" s="3"/>
+      <c r="Q311" s="3"/>
+      <c r="R311" s="3"/>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C312" s="2"/>
+      <c r="F312" s="2"/>
+      <c r="G312" s="2"/>
+      <c r="H312" s="2"/>
+      <c r="I312" s="2"/>
+      <c r="J312" s="2"/>
+      <c r="K312" s="2"/>
+      <c r="L312" s="5"/>
+      <c r="M312" s="2"/>
+      <c r="N312" s="5"/>
+      <c r="O312" s="2"/>
+      <c r="P312" s="2"/>
+      <c r="Q312" s="2"/>
+      <c r="R312" s="2"/>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A313" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="C313" s="3"/>
+      <c r="F313" s="3"/>
+      <c r="G313" s="3"/>
+      <c r="H313" s="3"/>
+      <c r="I313" s="3"/>
+      <c r="J313" s="3"/>
+      <c r="K313" s="3"/>
+      <c r="L313" s="6"/>
+      <c r="M313" s="3"/>
+      <c r="N313" s="6"/>
+      <c r="O313" s="3"/>
+      <c r="P313" s="3"/>
+      <c r="Q313" s="3"/>
+      <c r="R313" s="3"/>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A314" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="C314" s="2"/>
+      <c r="F314" s="2"/>
+      <c r="G314" s="2"/>
+      <c r="H314" s="2"/>
+      <c r="I314" s="2"/>
+      <c r="J314" s="2"/>
+      <c r="K314" s="2"/>
+      <c r="L314" s="5"/>
+      <c r="M314" s="2"/>
+      <c r="N314" s="5"/>
+      <c r="O314" s="2"/>
+      <c r="P314" s="2"/>
+      <c r="Q314" s="2"/>
+      <c r="R314" s="2"/>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A315" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="C315" s="3"/>
+      <c r="F315" s="3"/>
+      <c r="G315" s="3"/>
+      <c r="H315" s="3"/>
+      <c r="I315" s="3"/>
+      <c r="J315" s="3"/>
+      <c r="K315" s="3"/>
+      <c r="L315" s="6"/>
+      <c r="M315" s="3"/>
+      <c r="N315" s="6"/>
+      <c r="O315" s="3"/>
+      <c r="P315" s="3"/>
+      <c r="Q315" s="3"/>
+      <c r="R315" s="3"/>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A316" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C316" s="2"/>
+      <c r="F316" s="2"/>
+      <c r="G316" s="2"/>
+      <c r="H316" s="2"/>
+      <c r="I316" s="2"/>
+      <c r="J316" s="2"/>
+      <c r="K316" s="2"/>
+      <c r="L316" s="5"/>
+      <c r="M316" s="2"/>
+      <c r="N316" s="5"/>
+      <c r="O316" s="2"/>
+      <c r="P316" s="2"/>
+      <c r="Q316" s="2"/>
+      <c r="R316" s="2"/>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C317" s="3"/>
+      <c r="F317" s="3"/>
+      <c r="G317" s="3"/>
+      <c r="H317" s="3"/>
+      <c r="I317" s="3"/>
+      <c r="J317" s="3"/>
+      <c r="K317" s="3"/>
+      <c r="L317" s="6"/>
+      <c r="M317" s="3"/>
+      <c r="N317" s="6"/>
+      <c r="O317" s="3"/>
+      <c r="P317" s="3"/>
+      <c r="Q317" s="3"/>
+      <c r="R317" s="3"/>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A318" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C318" s="2"/>
+      <c r="F318" s="2"/>
+      <c r="G318" s="2"/>
+      <c r="H318" s="2"/>
+      <c r="I318" s="2"/>
+      <c r="J318" s="2"/>
+      <c r="K318" s="2"/>
+      <c r="L318" s="5"/>
+      <c r="M318" s="2"/>
+      <c r="N318" s="5"/>
+      <c r="O318" s="2"/>
+      <c r="P318" s="2"/>
+      <c r="Q318" s="2"/>
+      <c r="R318" s="2"/>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A319" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C319" s="3"/>
+      <c r="F319" s="3"/>
+      <c r="G319" s="3"/>
+      <c r="H319" s="3"/>
+      <c r="I319" s="3"/>
+      <c r="J319" s="3"/>
+      <c r="K319" s="3"/>
+      <c r="L319" s="6"/>
+      <c r="M319" s="3"/>
+      <c r="N319" s="6"/>
+      <c r="O319" s="3"/>
+      <c r="P319" s="3"/>
+      <c r="Q319" s="3"/>
+      <c r="R319" s="3"/>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A320" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C320" s="2"/>
+      <c r="F320" s="2"/>
+      <c r="G320" s="2"/>
+      <c r="H320" s="2"/>
+      <c r="I320" s="2"/>
+      <c r="J320" s="2"/>
+      <c r="K320" s="2"/>
+      <c r="L320" s="5"/>
+      <c r="M320" s="2"/>
+      <c r="N320" s="5"/>
+      <c r="O320" s="2"/>
+      <c r="P320" s="2"/>
+      <c r="Q320" s="2"/>
+      <c r="R320" s="2"/>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A321" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C321" s="3"/>
+      <c r="F321" s="3"/>
+      <c r="G321" s="3"/>
+      <c r="H321" s="3"/>
+      <c r="I321" s="3"/>
+      <c r="J321" s="3"/>
+      <c r="K321" s="3"/>
+      <c r="L321" s="6"/>
+      <c r="M321" s="3"/>
+      <c r="N321" s="6"/>
+      <c r="O321" s="3"/>
+      <c r="P321" s="3"/>
+      <c r="Q321" s="3"/>
+      <c r="R321" s="3"/>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A322" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C322" s="2"/>
+      <c r="F322" s="2"/>
+      <c r="G322" s="2"/>
+      <c r="H322" s="2"/>
+      <c r="I322" s="2"/>
+      <c r="J322" s="2"/>
+      <c r="K322" s="2"/>
+      <c r="L322" s="5"/>
+      <c r="M322" s="2"/>
+      <c r="N322" s="5"/>
+      <c r="O322" s="2"/>
+      <c r="P322" s="2"/>
+      <c r="Q322" s="2"/>
+      <c r="R322" s="2"/>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A323" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C323" s="3"/>
+      <c r="F323" s="3"/>
+      <c r="G323" s="3"/>
+      <c r="H323" s="3"/>
+      <c r="I323" s="3"/>
+      <c r="J323" s="3"/>
+      <c r="K323" s="3"/>
+      <c r="L323" s="6"/>
+      <c r="M323" s="3"/>
+      <c r="N323" s="6"/>
+      <c r="O323" s="3"/>
+      <c r="P323" s="3"/>
+      <c r="Q323" s="3"/>
+      <c r="R323" s="3"/>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A324" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="C324" s="2"/>
+      <c r="F324" s="2"/>
+      <c r="G324" s="2"/>
+      <c r="H324" s="2"/>
+      <c r="I324" s="2"/>
+      <c r="J324" s="2"/>
+      <c r="K324" s="2"/>
+      <c r="L324" s="5"/>
+      <c r="M324" s="2"/>
+      <c r="N324" s="5"/>
+      <c r="O324" s="2"/>
+      <c r="P324" s="2"/>
+      <c r="Q324" s="2"/>
+      <c r="R324" s="2"/>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A325" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C325" s="3"/>
+      <c r="F325" s="3"/>
+      <c r="G325" s="3"/>
+      <c r="H325" s="3"/>
+      <c r="I325" s="3"/>
+      <c r="J325" s="3"/>
+      <c r="K325" s="3"/>
+      <c r="L325" s="6"/>
+      <c r="M325" s="3"/>
+      <c r="N325" s="6"/>
+      <c r="O325" s="3"/>
+      <c r="P325" s="3"/>
+      <c r="Q325" s="3"/>
+      <c r="R325" s="3"/>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A326" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C326" s="2"/>
+      <c r="F326" s="2"/>
+      <c r="G326" s="2"/>
+      <c r="H326" s="2"/>
+      <c r="I326" s="2"/>
+      <c r="J326" s="2"/>
+      <c r="K326" s="2"/>
+      <c r="L326" s="5"/>
+      <c r="M326" s="2"/>
+      <c r="N326" s="5"/>
+      <c r="O326" s="2"/>
+      <c r="P326" s="2"/>
+      <c r="Q326" s="2"/>
+      <c r="R326" s="2"/>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A327" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C327" s="3"/>
+      <c r="F327" s="3"/>
+      <c r="G327" s="3"/>
+      <c r="H327" s="3"/>
+      <c r="I327" s="3"/>
+      <c r="J327" s="3"/>
+      <c r="K327" s="3"/>
+      <c r="L327" s="6"/>
+      <c r="M327" s="3"/>
+      <c r="N327" s="6"/>
+      <c r="O327" s="3"/>
+      <c r="P327" s="3"/>
+      <c r="Q327" s="3"/>
+      <c r="R327" s="3"/>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A328" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C328" s="2"/>
+      <c r="F328" s="2"/>
+      <c r="G328" s="2"/>
+      <c r="H328" s="2"/>
+      <c r="I328" s="2"/>
+      <c r="J328" s="2"/>
+      <c r="K328" s="2"/>
+      <c r="L328" s="5"/>
+      <c r="M328" s="2"/>
+      <c r="N328" s="5"/>
+      <c r="O328" s="2"/>
+      <c r="P328" s="2"/>
+      <c r="Q328" s="2"/>
+      <c r="R328" s="2"/>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A329" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C329" s="3"/>
+      <c r="F329" s="3"/>
+      <c r="G329" s="3"/>
+      <c r="H329" s="3"/>
+      <c r="I329" s="3"/>
+      <c r="J329" s="3"/>
+      <c r="K329" s="3"/>
+      <c r="L329" s="6"/>
+      <c r="M329" s="3"/>
+      <c r="N329" s="6"/>
+      <c r="O329" s="3"/>
+      <c r="P329" s="3"/>
+      <c r="Q329" s="3"/>
+      <c r="R329" s="3"/>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A330" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C330" s="2"/>
+      <c r="F330" s="2"/>
+      <c r="G330" s="2"/>
+      <c r="H330" s="2"/>
+      <c r="I330" s="2"/>
+      <c r="J330" s="2"/>
+      <c r="K330" s="2"/>
+      <c r="L330" s="5"/>
+      <c r="M330" s="2"/>
+      <c r="N330" s="5"/>
+      <c r="O330" s="2"/>
+      <c r="P330" s="2"/>
+      <c r="Q330" s="2"/>
+      <c r="R330" s="2"/>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B331" s="4"/>
+      <c r="C331" s="3"/>
+      <c r="F331" s="3"/>
+      <c r="G331" s="3"/>
+      <c r="H331" s="3"/>
+      <c r="I331" s="3"/>
+      <c r="J331" s="3"/>
+      <c r="K331" s="3"/>
+      <c r="L331" s="6"/>
+      <c r="M331" s="3"/>
+      <c r="N331" s="6"/>
+      <c r="O331" s="3"/>
+      <c r="P331" s="3"/>
+      <c r="Q331" s="3"/>
+      <c r="R331" s="3"/>
+    </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B332" s="4"/>
+      <c r="C332" s="2"/>
+      <c r="F332" s="2"/>
+      <c r="G332" s="2"/>
+      <c r="H332" s="2"/>
+      <c r="I332" s="2"/>
+      <c r="J332" s="2"/>
+      <c r="K332" s="2"/>
+      <c r="L332" s="5"/>
+      <c r="M332" s="2"/>
+      <c r="N332" s="5"/>
+      <c r="O332" s="2"/>
+      <c r="P332" s="2"/>
+      <c r="Q332" s="2"/>
+      <c r="R332" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Desktop\temp\seketala\cache\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D4D3D6-1B0E-4CA4-AF82-6262BA7B5F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CBF922-B4E7-436A-B806-78FD705E1D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1380" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="620">
   <si>
     <t>كد</t>
   </si>
@@ -816,12 +816,6 @@
     <t>2800008</t>
   </si>
   <si>
-    <t>2800012</t>
-  </si>
-  <si>
-    <t>2800001</t>
-  </si>
-  <si>
     <t>2800005</t>
   </si>
   <si>
@@ -1650,12 +1644,6 @@
     <t>آب نارنج</t>
   </si>
   <si>
-    <t>آب معدني 1.5 ليتري</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آب معدني </t>
-  </si>
-  <si>
     <t>آب گازدار</t>
   </si>
   <si>
@@ -1734,9 +1722,6 @@
     <t>1100065</t>
   </si>
   <si>
-    <t>1100066</t>
-  </si>
-  <si>
     <t>آب معدني 300 سي سي</t>
   </si>
   <si>
@@ -1897,6 +1882,9 @@
   </si>
   <si>
     <t>خانواده شاتوت</t>
+  </si>
+  <si>
+    <t>آب معدني</t>
   </si>
 </sst>
 </file>
@@ -2242,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R332"/>
+  <dimension ref="A1:R331"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -2254,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2262,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2270,7 +2258,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2278,7 +2266,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2286,7 +2274,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2294,7 +2282,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2302,7 +2290,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2310,7 +2298,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2318,7 +2306,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2326,7 +2314,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2334,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2342,7 +2330,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2350,7 +2338,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2358,7 +2346,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2366,7 +2354,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2374,7 +2362,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2382,7 +2370,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2390,7 +2378,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2398,7 +2386,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2406,7 +2394,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2414,7 +2402,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2422,7 +2410,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2430,7 +2418,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2438,7 +2426,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2446,7 +2434,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2454,7 +2442,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2462,7 +2450,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2470,7 +2458,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2478,7 +2466,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2486,7 +2474,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2494,7 +2482,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2502,7 +2490,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2510,7 +2498,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2518,7 +2506,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2526,7 +2514,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2534,7 +2522,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2542,7 +2530,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2550,7 +2538,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2558,7 +2546,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2566,7 +2554,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2574,7 +2562,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2582,7 +2570,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2590,7 +2578,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2598,7 +2586,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2606,7 +2594,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2614,7 +2602,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2622,7 +2610,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2630,7 +2618,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2638,7 +2626,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2646,7 +2634,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2654,7 +2642,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2662,7 +2650,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2670,7 +2658,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2678,7 +2666,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2686,7 +2674,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2694,7 +2682,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2702,7 +2690,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2710,7 +2698,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2718,7 +2706,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2726,7 +2714,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2734,7 +2722,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2742,7 +2730,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2750,7 +2738,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2758,7 +2746,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2766,7 +2754,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2774,7 +2762,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2782,7 +2770,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2790,7 +2778,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2798,7 +2786,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2806,7 +2794,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2814,7 +2802,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2822,7 +2810,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2830,7 +2818,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2838,7 +2826,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2846,7 +2834,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2854,7 +2842,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2862,7 +2850,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2870,7 +2858,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2878,7 +2866,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2886,7 +2874,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2894,7 +2882,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2902,7 +2890,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2910,7 +2898,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2918,7 +2906,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2926,7 +2914,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2934,7 +2922,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2942,7 +2930,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2950,7 +2938,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2958,7 +2946,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2966,7 +2954,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2974,7 +2962,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2982,7 +2970,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2990,7 +2978,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2998,7 +2986,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -3006,7 +2994,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -3014,7 +3002,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -3022,7 +3010,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -3030,7 +3018,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -3038,7 +3026,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -3046,7 +3034,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -3054,7 +3042,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -3062,7 +3050,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -3070,7 +3058,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -3078,7 +3066,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -3086,7 +3074,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -3094,7 +3082,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -3102,7 +3090,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -3110,7 +3098,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -3118,7 +3106,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -3126,7 +3114,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -3134,7 +3122,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -3142,7 +3130,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -3150,7 +3138,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -3158,7 +3146,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -3166,7 +3154,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -3174,7 +3162,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -3182,7 +3170,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -3190,7 +3178,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -3198,7 +3186,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -3206,7 +3194,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -3214,7 +3202,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -3222,7 +3210,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -3230,7 +3218,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -3238,7 +3226,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -3246,7 +3234,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -3254,7 +3242,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -3262,7 +3250,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -3270,7 +3258,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -3278,7 +3266,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -3286,7 +3274,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -3294,7 +3282,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -3302,7 +3290,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -3310,7 +3298,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -3318,7 +3306,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -3326,7 +3314,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -3334,7 +3322,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -3342,7 +3330,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -3350,7 +3338,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -3358,7 +3346,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -3366,7 +3354,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -3374,7 +3362,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -3382,7 +3370,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -3390,7 +3378,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -3398,7 +3386,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -3406,7 +3394,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -3414,7 +3402,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -3422,7 +3410,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -3430,7 +3418,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -3438,7 +3426,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3446,7 +3434,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3454,7 +3442,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -3462,7 +3450,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -3470,7 +3458,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -3478,7 +3466,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -3486,7 +3474,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -3494,7 +3482,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -3502,7 +3490,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -3510,7 +3498,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -3518,7 +3506,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -3526,7 +3514,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -3534,7 +3522,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -3542,7 +3530,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -3550,7 +3538,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -3558,7 +3546,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -3566,7 +3554,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -3574,7 +3562,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -3582,7 +3570,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -3590,7 +3578,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -3598,7 +3586,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -3606,7 +3594,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -3614,7 +3602,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -3622,7 +3610,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -3630,7 +3618,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3638,7 +3626,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -3646,7 +3634,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -3654,7 +3642,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -3662,7 +3650,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3670,7 +3658,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -3678,7 +3666,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3686,7 +3674,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -3694,7 +3682,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -3702,7 +3690,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3710,7 +3698,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -3718,7 +3706,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -3726,7 +3714,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -3734,7 +3722,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -3742,7 +3730,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -3750,7 +3738,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -3758,7 +3746,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -3766,7 +3754,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -3774,7 +3762,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3782,7 +3770,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3790,7 +3778,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3798,7 +3786,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3806,7 +3794,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3814,7 +3802,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3822,7 +3810,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3830,7 +3818,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3838,7 +3826,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3846,7 +3834,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3854,7 +3842,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3862,7 +3850,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3870,7 +3858,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3878,7 +3866,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3886,7 +3874,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3894,7 +3882,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3902,7 +3890,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3910,7 +3898,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -3918,7 +3906,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3926,7 +3914,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -3934,7 +3922,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -3942,7 +3930,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -3950,7 +3938,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -3958,7 +3946,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -3966,7 +3954,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -3974,7 +3962,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -3982,7 +3970,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -3990,7 +3978,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -3998,7 +3986,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -4006,7 +3994,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -4014,7 +4002,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -4022,7 +4010,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -4030,7 +4018,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -4038,7 +4026,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -4046,7 +4034,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -4054,7 +4042,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -4062,7 +4050,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -4070,7 +4058,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -4078,7 +4066,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -4086,7 +4074,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -4094,7 +4082,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -4102,7 +4090,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -4110,7 +4098,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -4118,7 +4106,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -4126,7 +4114,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -4134,7 +4122,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -4142,7 +4130,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -4150,7 +4138,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -4158,7 +4146,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -4166,7 +4154,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -4174,7 +4162,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -4182,7 +4170,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -4190,7 +4178,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -4198,7 +4186,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -4206,7 +4194,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -4214,7 +4202,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -4222,7 +4210,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -4230,7 +4218,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -4238,7 +4226,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -4246,7 +4234,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -4254,7 +4242,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -4262,7 +4250,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -4270,7 +4258,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -4278,7 +4266,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -4286,7 +4274,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -4294,7 +4282,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -4302,7 +4290,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -4310,7 +4298,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -4318,7 +4306,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -4326,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -4334,7 +4322,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -4342,7 +4330,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -4350,236 +4338,250 @@
         <v>262</v>
       </c>
       <c r="B263" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <v>1100066</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B266" s="3" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B264" s="2" t="s">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B265" s="3" t="s">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B268" s="3" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B266" s="2" t="s">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B267" s="3" t="s">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B270" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B268" s="2" t="s">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B269" s="3" t="s">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B272" s="3" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B270" s="2" t="s">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B273" s="2" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B271" s="3" t="s">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B274" s="3" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B272" s="2" t="s">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B273" s="3" t="s">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A276" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B276" s="3" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B274" s="2" t="s">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B277" s="2" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B275" s="3" t="s">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A278" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B278" s="3" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B276" s="2" t="s">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A279" s="2">
+        <v>2500013</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B280" s="3" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B279" s="3" t="s">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>1100057</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" s="2">
-        <v>2500013</v>
-      </c>
-      <c r="B280" s="2" t="s">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>1100059</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>1100038</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>2100021</v>
+      </c>
+      <c r="B284" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>1100062</v>
+      </c>
+      <c r="B285" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>1100061</v>
+      </c>
+      <c r="B286" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282">
-        <v>1100057</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283">
-        <v>1100059</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284">
-        <v>1100038</v>
-      </c>
-      <c r="B284" s="2" t="s">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>1100060</v>
+      </c>
+      <c r="B287" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285">
-        <v>2100021</v>
-      </c>
-      <c r="B285" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286">
-        <v>1100062</v>
-      </c>
-      <c r="B286" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287">
-        <v>1100061</v>
-      </c>
-      <c r="B287" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288">
-        <v>1100060</v>
-      </c>
-      <c r="B288" t="s">
-        <v>567</v>
-      </c>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A288" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C288" s="2"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="2"/>
+      <c r="H288" s="2"/>
+      <c r="I288" s="2"/>
+      <c r="J288" s="2"/>
+      <c r="K288" s="2"/>
+      <c r="L288" s="5"/>
+      <c r="M288" s="2"/>
+      <c r="N288" s="5"/>
+      <c r="O288" s="2"/>
+      <c r="P288" s="2"/>
+      <c r="Q288" s="2"/>
+      <c r="R288" s="2"/>
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A289" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B289" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="C289" s="2"/>
-      <c r="F289" s="2"/>
-      <c r="G289" s="2"/>
-      <c r="H289" s="2"/>
-      <c r="I289" s="2"/>
-      <c r="J289" s="2"/>
-      <c r="K289" s="2"/>
-      <c r="L289" s="5"/>
-      <c r="M289" s="2"/>
-      <c r="N289" s="5"/>
-      <c r="O289" s="2"/>
-      <c r="P289" s="2"/>
-      <c r="Q289" s="2"/>
-      <c r="R289" s="2"/>
+      <c r="A289" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C289" s="3"/>
+      <c r="F289" s="3"/>
+      <c r="G289" s="3"/>
+      <c r="H289" s="3"/>
+      <c r="I289" s="3"/>
+      <c r="J289" s="3"/>
+      <c r="K289" s="3"/>
+      <c r="L289" s="6"/>
+      <c r="M289" s="3"/>
+      <c r="N289" s="6"/>
+      <c r="O289" s="3"/>
+      <c r="P289" s="3"/>
+      <c r="Q289" s="3"/>
+      <c r="R289" s="3"/>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A290" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B290" s="2" t="s">
+      <c r="A290" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B290" s="3" t="s">
         <v>454</v>
       </c>
       <c r="C290" s="3"/>
@@ -4598,918 +4600,896 @@
       <c r="R290" s="3"/>
     </row>
     <row r="291" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A291" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="C291" s="3"/>
-      <c r="F291" s="3"/>
-      <c r="G291" s="3"/>
-      <c r="H291" s="3"/>
-      <c r="I291" s="3"/>
-      <c r="J291" s="3"/>
-      <c r="K291" s="3"/>
-      <c r="L291" s="6"/>
-      <c r="M291" s="3"/>
-      <c r="N291" s="6"/>
-      <c r="O291" s="3"/>
-      <c r="P291" s="3"/>
-      <c r="Q291" s="3"/>
-      <c r="R291" s="3"/>
+      <c r="A291" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="2"/>
+      <c r="I291" s="2"/>
+      <c r="J291" s="2"/>
+      <c r="K291" s="2"/>
+      <c r="L291" s="5"/>
+      <c r="M291" s="2"/>
+      <c r="N291" s="5"/>
+      <c r="O291" s="2"/>
+      <c r="P291" s="2"/>
+      <c r="Q291" s="2"/>
+      <c r="R291" s="2"/>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A292" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="C292" s="2"/>
-      <c r="F292" s="2"/>
-      <c r="G292" s="2"/>
-      <c r="H292" s="2"/>
-      <c r="I292" s="2"/>
-      <c r="J292" s="2"/>
-      <c r="K292" s="2"/>
-      <c r="L292" s="5"/>
-      <c r="M292" s="2"/>
-      <c r="N292" s="5"/>
-      <c r="O292" s="2"/>
-      <c r="P292" s="2"/>
-      <c r="Q292" s="2"/>
-      <c r="R292" s="2"/>
+      <c r="A292" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C292" s="3"/>
+      <c r="F292" s="3"/>
+      <c r="G292" s="3"/>
+      <c r="H292" s="3"/>
+      <c r="I292" s="3"/>
+      <c r="J292" s="3"/>
+      <c r="K292" s="3"/>
+      <c r="L292" s="6"/>
+      <c r="M292" s="3"/>
+      <c r="N292" s="6"/>
+      <c r="O292" s="3"/>
+      <c r="P292" s="3"/>
+      <c r="Q292" s="3"/>
+      <c r="R292" s="3"/>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A293" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B293" s="3" t="s">
+      <c r="A293" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C293" s="2"/>
+      <c r="F293" s="2"/>
+      <c r="G293" s="2"/>
+      <c r="H293" s="2"/>
+      <c r="I293" s="2"/>
+      <c r="J293" s="2"/>
+      <c r="K293" s="2"/>
+      <c r="L293" s="5"/>
+      <c r="M293" s="2"/>
+      <c r="N293" s="5"/>
+      <c r="O293" s="2"/>
+      <c r="P293" s="2"/>
+      <c r="Q293" s="2"/>
+      <c r="R293" s="2"/>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A294" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C294" s="3"/>
+      <c r="F294" s="3"/>
+      <c r="G294" s="3"/>
+      <c r="H294" s="3"/>
+      <c r="I294" s="3"/>
+      <c r="J294" s="3"/>
+      <c r="K294" s="3"/>
+      <c r="L294" s="6"/>
+      <c r="M294" s="3"/>
+      <c r="N294" s="6"/>
+      <c r="O294" s="3"/>
+      <c r="P294" s="3"/>
+      <c r="Q294" s="3"/>
+      <c r="R294" s="3"/>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C293" s="3"/>
-      <c r="F293" s="3"/>
-      <c r="G293" s="3"/>
-      <c r="H293" s="3"/>
-      <c r="I293" s="3"/>
-      <c r="J293" s="3"/>
-      <c r="K293" s="3"/>
-      <c r="L293" s="6"/>
-      <c r="M293" s="3"/>
-      <c r="N293" s="6"/>
-      <c r="O293" s="3"/>
-      <c r="P293" s="3"/>
-      <c r="Q293" s="3"/>
-      <c r="R293" s="3"/>
-    </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A294" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C294" s="2"/>
-      <c r="F294" s="2"/>
-      <c r="G294" s="2"/>
-      <c r="H294" s="2"/>
-      <c r="I294" s="2"/>
-      <c r="J294" s="2"/>
-      <c r="K294" s="2"/>
-      <c r="L294" s="5"/>
-      <c r="M294" s="2"/>
-      <c r="N294" s="5"/>
-      <c r="O294" s="2"/>
-      <c r="P294" s="2"/>
-      <c r="Q294" s="2"/>
-      <c r="R294" s="2"/>
-    </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A295" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B295" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C295" s="3"/>
-      <c r="F295" s="3"/>
-      <c r="G295" s="3"/>
-      <c r="H295" s="3"/>
-      <c r="I295" s="3"/>
-      <c r="J295" s="3"/>
-      <c r="K295" s="3"/>
-      <c r="L295" s="6"/>
-      <c r="M295" s="3"/>
-      <c r="N295" s="6"/>
-      <c r="O295" s="3"/>
-      <c r="P295" s="3"/>
-      <c r="Q295" s="3"/>
-      <c r="R295" s="3"/>
+      <c r="C295" s="2"/>
+      <c r="F295" s="2"/>
+      <c r="G295" s="2"/>
+      <c r="H295" s="2"/>
+      <c r="I295" s="2"/>
+      <c r="J295" s="2"/>
+      <c r="K295" s="2"/>
+      <c r="L295" s="5"/>
+      <c r="M295" s="2"/>
+      <c r="N295" s="5"/>
+      <c r="O295" s="2"/>
+      <c r="P295" s="2"/>
+      <c r="Q295" s="2"/>
+      <c r="R295" s="2"/>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C296" s="2"/>
-      <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-      <c r="H296" s="2"/>
-      <c r="I296" s="2"/>
-      <c r="J296" s="2"/>
-      <c r="K296" s="2"/>
-      <c r="L296" s="5"/>
-      <c r="M296" s="2"/>
-      <c r="N296" s="5"/>
-      <c r="O296" s="2"/>
-      <c r="P296" s="2"/>
-      <c r="Q296" s="2"/>
-      <c r="R296" s="2"/>
+      <c r="A296" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C296" s="3"/>
+      <c r="F296" s="3"/>
+      <c r="G296" s="3"/>
+      <c r="H296" s="3"/>
+      <c r="I296" s="3"/>
+      <c r="J296" s="3"/>
+      <c r="K296" s="3"/>
+      <c r="L296" s="6"/>
+      <c r="M296" s="3"/>
+      <c r="N296" s="6"/>
+      <c r="O296" s="3"/>
+      <c r="P296" s="3"/>
+      <c r="Q296" s="3"/>
+      <c r="R296" s="3"/>
     </row>
     <row r="297" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A297" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B297" s="3" t="s">
+      <c r="A297" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C297" s="3"/>
-      <c r="F297" s="3"/>
-      <c r="G297" s="3"/>
-      <c r="H297" s="3"/>
-      <c r="I297" s="3"/>
-      <c r="J297" s="3"/>
-      <c r="K297" s="3"/>
-      <c r="L297" s="6"/>
-      <c r="M297" s="3"/>
-      <c r="N297" s="6"/>
-      <c r="O297" s="3"/>
-      <c r="P297" s="3"/>
-      <c r="Q297" s="3"/>
-      <c r="R297" s="3"/>
+      <c r="C297" s="2"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="2"/>
+      <c r="H297" s="2"/>
+      <c r="I297" s="2"/>
+      <c r="J297" s="2"/>
+      <c r="K297" s="2"/>
+      <c r="L297" s="5"/>
+      <c r="M297" s="2"/>
+      <c r="N297" s="5"/>
+      <c r="O297" s="2"/>
+      <c r="P297" s="2"/>
+      <c r="Q297" s="2"/>
+      <c r="R297" s="2"/>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A298" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C298" s="2"/>
-      <c r="F298" s="2"/>
-      <c r="G298" s="2"/>
-      <c r="H298" s="2"/>
-      <c r="I298" s="2"/>
-      <c r="J298" s="2"/>
-      <c r="K298" s="2"/>
-      <c r="L298" s="5"/>
-      <c r="M298" s="2"/>
-      <c r="N298" s="5"/>
-      <c r="O298" s="2"/>
-      <c r="P298" s="2"/>
-      <c r="Q298" s="2"/>
-      <c r="R298" s="2"/>
+      <c r="A298" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C298" s="3"/>
+      <c r="F298" s="3"/>
+      <c r="G298" s="3"/>
+      <c r="H298" s="3"/>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="6"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="6"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="3"/>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A299" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B299" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C299" s="3"/>
-      <c r="F299" s="3"/>
-      <c r="G299" s="3"/>
-      <c r="H299" s="3"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="3"/>
-      <c r="K299" s="3"/>
-      <c r="L299" s="6"/>
-      <c r="M299" s="3"/>
-      <c r="N299" s="6"/>
-      <c r="O299" s="3"/>
-      <c r="P299" s="3"/>
-      <c r="Q299" s="3"/>
-      <c r="R299" s="3"/>
+      <c r="A299" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C299" s="2"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
+      <c r="H299" s="2"/>
+      <c r="I299" s="2"/>
+      <c r="J299" s="2"/>
+      <c r="K299" s="2"/>
+      <c r="L299" s="5"/>
+      <c r="M299" s="2"/>
+      <c r="N299" s="5"/>
+      <c r="O299" s="2"/>
+      <c r="P299" s="2"/>
+      <c r="Q299" s="2"/>
+      <c r="R299" s="2"/>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B300" s="2" t="s">
+      <c r="A300" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C300" s="3"/>
+      <c r="F300" s="3"/>
+      <c r="G300" s="3"/>
+      <c r="H300" s="3"/>
+      <c r="I300" s="3"/>
+      <c r="J300" s="3"/>
+      <c r="K300" s="3"/>
+      <c r="L300" s="6"/>
+      <c r="M300" s="3"/>
+      <c r="N300" s="6"/>
+      <c r="O300" s="3"/>
+      <c r="P300" s="3"/>
+      <c r="Q300" s="3"/>
+      <c r="R300" s="3"/>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C301" s="2"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="2"/>
+      <c r="H301" s="2"/>
+      <c r="I301" s="2"/>
+      <c r="J301" s="2"/>
+      <c r="K301" s="2"/>
+      <c r="L301" s="5"/>
+      <c r="M301" s="2"/>
+      <c r="N301" s="5"/>
+      <c r="O301" s="2"/>
+      <c r="P301" s="2"/>
+      <c r="Q301" s="2"/>
+      <c r="R301" s="2"/>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C302" s="3"/>
+      <c r="F302" s="3"/>
+      <c r="G302" s="3"/>
+      <c r="H302" s="3"/>
+      <c r="I302" s="3"/>
+      <c r="J302" s="3"/>
+      <c r="K302" s="3"/>
+      <c r="L302" s="6"/>
+      <c r="M302" s="3"/>
+      <c r="N302" s="6"/>
+      <c r="O302" s="3"/>
+      <c r="P302" s="3"/>
+      <c r="Q302" s="3"/>
+      <c r="R302" s="3"/>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C303" s="2"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="2"/>
+      <c r="H303" s="2"/>
+      <c r="I303" s="2"/>
+      <c r="J303" s="2"/>
+      <c r="K303" s="2"/>
+      <c r="L303" s="5"/>
+      <c r="M303" s="2"/>
+      <c r="N303" s="5"/>
+      <c r="O303" s="2"/>
+      <c r="P303" s="2"/>
+      <c r="Q303" s="2"/>
+      <c r="R303" s="2"/>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="C300" s="2"/>
-      <c r="F300" s="2"/>
-      <c r="G300" s="2"/>
-      <c r="H300" s="2"/>
-      <c r="I300" s="2"/>
-      <c r="J300" s="2"/>
-      <c r="K300" s="2"/>
-      <c r="L300" s="5"/>
-      <c r="M300" s="2"/>
-      <c r="N300" s="5"/>
-      <c r="O300" s="2"/>
-      <c r="P300" s="2"/>
-      <c r="Q300" s="2"/>
-      <c r="R300" s="2"/>
-    </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A301" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C301" s="3"/>
-      <c r="F301" s="3"/>
-      <c r="G301" s="3"/>
-      <c r="H301" s="3"/>
-      <c r="I301" s="3"/>
-      <c r="J301" s="3"/>
-      <c r="K301" s="3"/>
-      <c r="L301" s="6"/>
-      <c r="M301" s="3"/>
-      <c r="N301" s="6"/>
-      <c r="O301" s="3"/>
-      <c r="P301" s="3"/>
-      <c r="Q301" s="3"/>
-      <c r="R301" s="3"/>
-    </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A302" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="C302" s="2"/>
-      <c r="F302" s="2"/>
-      <c r="G302" s="2"/>
-      <c r="H302" s="2"/>
-      <c r="I302" s="2"/>
-      <c r="J302" s="2"/>
-      <c r="K302" s="2"/>
-      <c r="L302" s="5"/>
-      <c r="M302" s="2"/>
-      <c r="N302" s="5"/>
-      <c r="O302" s="2"/>
-      <c r="P302" s="2"/>
-      <c r="Q302" s="2"/>
-      <c r="R302" s="2"/>
-    </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A303" s="3" t="s">
+      <c r="B304" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B303" s="3" t="s">
+      <c r="C304" s="3"/>
+      <c r="F304" s="3"/>
+      <c r="G304" s="3"/>
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+      <c r="J304" s="3"/>
+      <c r="K304" s="3"/>
+      <c r="L304" s="6"/>
+      <c r="M304" s="3"/>
+      <c r="N304" s="6"/>
+      <c r="O304" s="3"/>
+      <c r="P304" s="3"/>
+      <c r="Q304" s="3"/>
+      <c r="R304" s="3"/>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="C303" s="3"/>
-      <c r="F303" s="3"/>
-      <c r="G303" s="3"/>
-      <c r="H303" s="3"/>
-      <c r="I303" s="3"/>
-      <c r="J303" s="3"/>
-      <c r="K303" s="3"/>
-      <c r="L303" s="6"/>
-      <c r="M303" s="3"/>
-      <c r="N303" s="6"/>
-      <c r="O303" s="3"/>
-      <c r="P303" s="3"/>
-      <c r="Q303" s="3"/>
-      <c r="R303" s="3"/>
-    </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A304" s="2" t="s">
+      <c r="B305" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B304" s="2" t="s">
+      <c r="C305" s="2"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="2"/>
+      <c r="H305" s="2"/>
+      <c r="I305" s="2"/>
+      <c r="J305" s="2"/>
+      <c r="K305" s="2"/>
+      <c r="L305" s="5"/>
+      <c r="M305" s="2"/>
+      <c r="N305" s="5"/>
+      <c r="O305" s="2"/>
+      <c r="P305" s="2"/>
+      <c r="Q305" s="2"/>
+      <c r="R305" s="2"/>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="C304" s="2"/>
-      <c r="F304" s="2"/>
-      <c r="G304" s="2"/>
-      <c r="H304" s="2"/>
-      <c r="I304" s="2"/>
-      <c r="J304" s="2"/>
-      <c r="K304" s="2"/>
-      <c r="L304" s="5"/>
-      <c r="M304" s="2"/>
-      <c r="N304" s="5"/>
-      <c r="O304" s="2"/>
-      <c r="P304" s="2"/>
-      <c r="Q304" s="2"/>
-      <c r="R304" s="2"/>
-    </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A305" s="3" t="s">
+      <c r="B306" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="B305" s="3" t="s">
+      <c r="C306" s="3"/>
+      <c r="F306" s="3"/>
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
+      <c r="K306" s="3"/>
+      <c r="L306" s="6"/>
+      <c r="M306" s="3"/>
+      <c r="N306" s="6"/>
+      <c r="O306" s="3"/>
+      <c r="P306" s="3"/>
+      <c r="Q306" s="3"/>
+      <c r="R306" s="3"/>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C305" s="3"/>
-      <c r="F305" s="3"/>
-      <c r="G305" s="3"/>
-      <c r="H305" s="3"/>
-      <c r="I305" s="3"/>
-      <c r="J305" s="3"/>
-      <c r="K305" s="3"/>
-      <c r="L305" s="6"/>
-      <c r="M305" s="3"/>
-      <c r="N305" s="6"/>
-      <c r="O305" s="3"/>
-      <c r="P305" s="3"/>
-      <c r="Q305" s="3"/>
-      <c r="R305" s="3"/>
-    </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A306" s="2" t="s">
+      <c r="B307" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="B306" s="2" t="s">
+      <c r="C307" s="2"/>
+      <c r="F307" s="2"/>
+      <c r="G307" s="2"/>
+      <c r="H307" s="2"/>
+      <c r="I307" s="2"/>
+      <c r="J307" s="2"/>
+      <c r="K307" s="2"/>
+      <c r="L307" s="5"/>
+      <c r="M307" s="2"/>
+      <c r="N307" s="5"/>
+      <c r="O307" s="2"/>
+      <c r="P307" s="2"/>
+      <c r="Q307" s="2"/>
+      <c r="R307" s="2"/>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="C306" s="2"/>
-      <c r="F306" s="2"/>
-      <c r="G306" s="2"/>
-      <c r="H306" s="2"/>
-      <c r="I306" s="2"/>
-      <c r="J306" s="2"/>
-      <c r="K306" s="2"/>
-      <c r="L306" s="5"/>
-      <c r="M306" s="2"/>
-      <c r="N306" s="5"/>
-      <c r="O306" s="2"/>
-      <c r="P306" s="2"/>
-      <c r="Q306" s="2"/>
-      <c r="R306" s="2"/>
-    </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A307" s="3" t="s">
+      <c r="B308" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B307" s="3" t="s">
+      <c r="C308" s="3"/>
+      <c r="F308" s="3"/>
+      <c r="G308" s="3"/>
+      <c r="H308" s="3"/>
+      <c r="I308" s="3"/>
+      <c r="J308" s="3"/>
+      <c r="K308" s="3"/>
+      <c r="L308" s="6"/>
+      <c r="M308" s="3"/>
+      <c r="N308" s="6"/>
+      <c r="O308" s="3"/>
+      <c r="P308" s="3"/>
+      <c r="Q308" s="3"/>
+      <c r="R308" s="3"/>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A309" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="C307" s="3"/>
-      <c r="F307" s="3"/>
-      <c r="G307" s="3"/>
-      <c r="H307" s="3"/>
-      <c r="I307" s="3"/>
-      <c r="J307" s="3"/>
-      <c r="K307" s="3"/>
-      <c r="L307" s="6"/>
-      <c r="M307" s="3"/>
-      <c r="N307" s="6"/>
-      <c r="O307" s="3"/>
-      <c r="P307" s="3"/>
-      <c r="Q307" s="3"/>
-      <c r="R307" s="3"/>
-    </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A308" s="2" t="s">
+      <c r="B309" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B308" s="2" t="s">
+      <c r="C309" s="2"/>
+      <c r="F309" s="2"/>
+      <c r="G309" s="2"/>
+      <c r="H309" s="2"/>
+      <c r="I309" s="2"/>
+      <c r="J309" s="2"/>
+      <c r="K309" s="2"/>
+      <c r="L309" s="5"/>
+      <c r="M309" s="2"/>
+      <c r="N309" s="5"/>
+      <c r="O309" s="2"/>
+      <c r="P309" s="2"/>
+      <c r="Q309" s="2"/>
+      <c r="R309" s="2"/>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="C308" s="2"/>
-      <c r="F308" s="2"/>
-      <c r="G308" s="2"/>
-      <c r="H308" s="2"/>
-      <c r="I308" s="2"/>
-      <c r="J308" s="2"/>
-      <c r="K308" s="2"/>
-      <c r="L308" s="5"/>
-      <c r="M308" s="2"/>
-      <c r="N308" s="5"/>
-      <c r="O308" s="2"/>
-      <c r="P308" s="2"/>
-      <c r="Q308" s="2"/>
-      <c r="R308" s="2"/>
-    </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A309" s="3" t="s">
+      <c r="B310" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B309" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="C309" s="3"/>
-      <c r="F309" s="3"/>
-      <c r="G309" s="3"/>
-      <c r="H309" s="3"/>
-      <c r="I309" s="3"/>
-      <c r="J309" s="3"/>
-      <c r="K309" s="3"/>
-      <c r="L309" s="6"/>
-      <c r="M309" s="3"/>
-      <c r="N309" s="6"/>
-      <c r="O309" s="3"/>
-      <c r="P309" s="3"/>
-      <c r="Q309" s="3"/>
-      <c r="R309" s="3"/>
-    </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A310" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C310" s="2"/>
-      <c r="F310" s="2"/>
-      <c r="G310" s="2"/>
-      <c r="H310" s="2"/>
-      <c r="I310" s="2"/>
-      <c r="J310" s="2"/>
-      <c r="K310" s="2"/>
-      <c r="L310" s="5"/>
-      <c r="M310" s="2"/>
-      <c r="N310" s="5"/>
-      <c r="O310" s="2"/>
-      <c r="P310" s="2"/>
-      <c r="Q310" s="2"/>
-      <c r="R310" s="2"/>
+      <c r="C310" s="3"/>
+      <c r="F310" s="3"/>
+      <c r="G310" s="3"/>
+      <c r="H310" s="3"/>
+      <c r="I310" s="3"/>
+      <c r="J310" s="3"/>
+      <c r="K310" s="3"/>
+      <c r="L310" s="6"/>
+      <c r="M310" s="3"/>
+      <c r="N310" s="6"/>
+      <c r="O310" s="3"/>
+      <c r="P310" s="3"/>
+      <c r="Q310" s="3"/>
+      <c r="R310" s="3"/>
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A311" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="B311" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="C311" s="3"/>
-      <c r="F311" s="3"/>
-      <c r="G311" s="3"/>
-      <c r="H311" s="3"/>
-      <c r="I311" s="3"/>
-      <c r="J311" s="3"/>
-      <c r="K311" s="3"/>
-      <c r="L311" s="6"/>
-      <c r="M311" s="3"/>
-      <c r="N311" s="6"/>
-      <c r="O311" s="3"/>
-      <c r="P311" s="3"/>
-      <c r="Q311" s="3"/>
-      <c r="R311" s="3"/>
+      <c r="A311" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C311" s="2"/>
+      <c r="F311" s="2"/>
+      <c r="G311" s="2"/>
+      <c r="H311" s="2"/>
+      <c r="I311" s="2"/>
+      <c r="J311" s="2"/>
+      <c r="K311" s="2"/>
+      <c r="L311" s="5"/>
+      <c r="M311" s="2"/>
+      <c r="N311" s="5"/>
+      <c r="O311" s="2"/>
+      <c r="P311" s="2"/>
+      <c r="Q311" s="2"/>
+      <c r="R311" s="2"/>
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A312" s="2" t="s">
+      <c r="A312" s="3">
+        <v>1100066</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C312" s="3"/>
+      <c r="F312" s="3"/>
+      <c r="G312" s="3"/>
+      <c r="H312" s="3"/>
+      <c r="I312" s="3"/>
+      <c r="J312" s="3"/>
+      <c r="K312" s="3"/>
+      <c r="L312" s="6"/>
+      <c r="M312" s="3"/>
+      <c r="N312" s="6"/>
+      <c r="O312" s="3"/>
+      <c r="P312" s="3"/>
+      <c r="Q312" s="3"/>
+      <c r="R312" s="3"/>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C313" s="2"/>
+      <c r="F313" s="2"/>
+      <c r="G313" s="2"/>
+      <c r="H313" s="2"/>
+      <c r="I313" s="2"/>
+      <c r="J313" s="2"/>
+      <c r="K313" s="2"/>
+      <c r="L313" s="5"/>
+      <c r="M313" s="2"/>
+      <c r="N313" s="5"/>
+      <c r="O313" s="2"/>
+      <c r="P313" s="2"/>
+      <c r="Q313" s="2"/>
+      <c r="R313" s="2"/>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="C312" s="2"/>
-      <c r="F312" s="2"/>
-      <c r="G312" s="2"/>
-      <c r="H312" s="2"/>
-      <c r="I312" s="2"/>
-      <c r="J312" s="2"/>
-      <c r="K312" s="2"/>
-      <c r="L312" s="5"/>
-      <c r="M312" s="2"/>
-      <c r="N312" s="5"/>
-      <c r="O312" s="2"/>
-      <c r="P312" s="2"/>
-      <c r="Q312" s="2"/>
-      <c r="R312" s="2"/>
-    </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A313" s="3" t="s">
+      <c r="B314" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B313" s="3" t="s">
+      <c r="C314" s="3"/>
+      <c r="F314" s="3"/>
+      <c r="G314" s="3"/>
+      <c r="H314" s="3"/>
+      <c r="I314" s="3"/>
+      <c r="J314" s="3"/>
+      <c r="K314" s="3"/>
+      <c r="L314" s="6"/>
+      <c r="M314" s="3"/>
+      <c r="N314" s="6"/>
+      <c r="O314" s="3"/>
+      <c r="P314" s="3"/>
+      <c r="Q314" s="3"/>
+      <c r="R314" s="3"/>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C313" s="3"/>
-      <c r="F313" s="3"/>
-      <c r="G313" s="3"/>
-      <c r="H313" s="3"/>
-      <c r="I313" s="3"/>
-      <c r="J313" s="3"/>
-      <c r="K313" s="3"/>
-      <c r="L313" s="6"/>
-      <c r="M313" s="3"/>
-      <c r="N313" s="6"/>
-      <c r="O313" s="3"/>
-      <c r="P313" s="3"/>
-      <c r="Q313" s="3"/>
-      <c r="R313" s="3"/>
-    </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A314" s="2" t="s">
+      <c r="B315" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="C315" s="2"/>
+      <c r="F315" s="2"/>
+      <c r="G315" s="2"/>
+      <c r="H315" s="2"/>
+      <c r="I315" s="2"/>
+      <c r="J315" s="2"/>
+      <c r="K315" s="2"/>
+      <c r="L315" s="5"/>
+      <c r="M315" s="2"/>
+      <c r="N315" s="5"/>
+      <c r="O315" s="2"/>
+      <c r="P315" s="2"/>
+      <c r="Q315" s="2"/>
+      <c r="R315" s="2"/>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="C314" s="2"/>
-      <c r="F314" s="2"/>
-      <c r="G314" s="2"/>
-      <c r="H314" s="2"/>
-      <c r="I314" s="2"/>
-      <c r="J314" s="2"/>
-      <c r="K314" s="2"/>
-      <c r="L314" s="5"/>
-      <c r="M314" s="2"/>
-      <c r="N314" s="5"/>
-      <c r="O314" s="2"/>
-      <c r="P314" s="2"/>
-      <c r="Q314" s="2"/>
-      <c r="R314" s="2"/>
-    </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A315" s="3" t="s">
+      <c r="B316" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B315" s="3" t="s">
+      <c r="C316" s="3"/>
+      <c r="F316" s="3"/>
+      <c r="G316" s="3"/>
+      <c r="H316" s="3"/>
+      <c r="I316" s="3"/>
+      <c r="J316" s="3"/>
+      <c r="K316" s="3"/>
+      <c r="L316" s="6"/>
+      <c r="M316" s="3"/>
+      <c r="N316" s="6"/>
+      <c r="O316" s="3"/>
+      <c r="P316" s="3"/>
+      <c r="Q316" s="3"/>
+      <c r="R316" s="3"/>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C315" s="3"/>
-      <c r="F315" s="3"/>
-      <c r="G315" s="3"/>
-      <c r="H315" s="3"/>
-      <c r="I315" s="3"/>
-      <c r="J315" s="3"/>
-      <c r="K315" s="3"/>
-      <c r="L315" s="6"/>
-      <c r="M315" s="3"/>
-      <c r="N315" s="6"/>
-      <c r="O315" s="3"/>
-      <c r="P315" s="3"/>
-      <c r="Q315" s="3"/>
-      <c r="R315" s="3"/>
-    </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A316" s="2" t="s">
+      <c r="B317" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="C317" s="2"/>
+      <c r="F317" s="2"/>
+      <c r="G317" s="2"/>
+      <c r="H317" s="2"/>
+      <c r="I317" s="2"/>
+      <c r="J317" s="2"/>
+      <c r="K317" s="2"/>
+      <c r="L317" s="5"/>
+      <c r="M317" s="2"/>
+      <c r="N317" s="5"/>
+      <c r="O317" s="2"/>
+      <c r="P317" s="2"/>
+      <c r="Q317" s="2"/>
+      <c r="R317" s="2"/>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A318" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="C316" s="2"/>
-      <c r="F316" s="2"/>
-      <c r="G316" s="2"/>
-      <c r="H316" s="2"/>
-      <c r="I316" s="2"/>
-      <c r="J316" s="2"/>
-      <c r="K316" s="2"/>
-      <c r="L316" s="5"/>
-      <c r="M316" s="2"/>
-      <c r="N316" s="5"/>
-      <c r="O316" s="2"/>
-      <c r="P316" s="2"/>
-      <c r="Q316" s="2"/>
-      <c r="R316" s="2"/>
-    </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A317" s="3" t="s">
+      <c r="B318" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B317" s="3" t="s">
+      <c r="C318" s="3"/>
+      <c r="F318" s="3"/>
+      <c r="G318" s="3"/>
+      <c r="H318" s="3"/>
+      <c r="I318" s="3"/>
+      <c r="J318" s="3"/>
+      <c r="K318" s="3"/>
+      <c r="L318" s="6"/>
+      <c r="M318" s="3"/>
+      <c r="N318" s="6"/>
+      <c r="O318" s="3"/>
+      <c r="P318" s="3"/>
+      <c r="Q318" s="3"/>
+      <c r="R318" s="3"/>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A319" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="C317" s="3"/>
-      <c r="F317" s="3"/>
-      <c r="G317" s="3"/>
-      <c r="H317" s="3"/>
-      <c r="I317" s="3"/>
-      <c r="J317" s="3"/>
-      <c r="K317" s="3"/>
-      <c r="L317" s="6"/>
-      <c r="M317" s="3"/>
-      <c r="N317" s="6"/>
-      <c r="O317" s="3"/>
-      <c r="P317" s="3"/>
-      <c r="Q317" s="3"/>
-      <c r="R317" s="3"/>
-    </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A318" s="2" t="s">
+      <c r="B319" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B318" s="2" t="s">
+      <c r="C319" s="2"/>
+      <c r="F319" s="2"/>
+      <c r="G319" s="2"/>
+      <c r="H319" s="2"/>
+      <c r="I319" s="2"/>
+      <c r="J319" s="2"/>
+      <c r="K319" s="2"/>
+      <c r="L319" s="5"/>
+      <c r="M319" s="2"/>
+      <c r="N319" s="5"/>
+      <c r="O319" s="2"/>
+      <c r="P319" s="2"/>
+      <c r="Q319" s="2"/>
+      <c r="R319" s="2"/>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="C318" s="2"/>
-      <c r="F318" s="2"/>
-      <c r="G318" s="2"/>
-      <c r="H318" s="2"/>
-      <c r="I318" s="2"/>
-      <c r="J318" s="2"/>
-      <c r="K318" s="2"/>
-      <c r="L318" s="5"/>
-      <c r="M318" s="2"/>
-      <c r="N318" s="5"/>
-      <c r="O318" s="2"/>
-      <c r="P318" s="2"/>
-      <c r="Q318" s="2"/>
-      <c r="R318" s="2"/>
-    </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A319" s="3" t="s">
+      <c r="B320" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B319" s="3" t="s">
+      <c r="C320" s="3"/>
+      <c r="F320" s="3"/>
+      <c r="G320" s="3"/>
+      <c r="H320" s="3"/>
+      <c r="I320" s="3"/>
+      <c r="J320" s="3"/>
+      <c r="K320" s="3"/>
+      <c r="L320" s="6"/>
+      <c r="M320" s="3"/>
+      <c r="N320" s="6"/>
+      <c r="O320" s="3"/>
+      <c r="P320" s="3"/>
+      <c r="Q320" s="3"/>
+      <c r="R320" s="3"/>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="C319" s="3"/>
-      <c r="F319" s="3"/>
-      <c r="G319" s="3"/>
-      <c r="H319" s="3"/>
-      <c r="I319" s="3"/>
-      <c r="J319" s="3"/>
-      <c r="K319" s="3"/>
-      <c r="L319" s="6"/>
-      <c r="M319" s="3"/>
-      <c r="N319" s="6"/>
-      <c r="O319" s="3"/>
-      <c r="P319" s="3"/>
-      <c r="Q319" s="3"/>
-      <c r="R319" s="3"/>
-    </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A320" s="2" t="s">
+      <c r="B321" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B320" s="2" t="s">
+      <c r="C321" s="2"/>
+      <c r="F321" s="2"/>
+      <c r="G321" s="2"/>
+      <c r="H321" s="2"/>
+      <c r="I321" s="2"/>
+      <c r="J321" s="2"/>
+      <c r="K321" s="2"/>
+      <c r="L321" s="5"/>
+      <c r="M321" s="2"/>
+      <c r="N321" s="5"/>
+      <c r="O321" s="2"/>
+      <c r="P321" s="2"/>
+      <c r="Q321" s="2"/>
+      <c r="R321" s="2"/>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="C320" s="2"/>
-      <c r="F320" s="2"/>
-      <c r="G320" s="2"/>
-      <c r="H320" s="2"/>
-      <c r="I320" s="2"/>
-      <c r="J320" s="2"/>
-      <c r="K320" s="2"/>
-      <c r="L320" s="5"/>
-      <c r="M320" s="2"/>
-      <c r="N320" s="5"/>
-      <c r="O320" s="2"/>
-      <c r="P320" s="2"/>
-      <c r="Q320" s="2"/>
-      <c r="R320" s="2"/>
-    </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A321" s="3" t="s">
+      <c r="B322" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="B321" s="3" t="s">
+      <c r="C322" s="3"/>
+      <c r="F322" s="3"/>
+      <c r="G322" s="3"/>
+      <c r="H322" s="3"/>
+      <c r="I322" s="3"/>
+      <c r="J322" s="3"/>
+      <c r="K322" s="3"/>
+      <c r="L322" s="6"/>
+      <c r="M322" s="3"/>
+      <c r="N322" s="6"/>
+      <c r="O322" s="3"/>
+      <c r="P322" s="3"/>
+      <c r="Q322" s="3"/>
+      <c r="R322" s="3"/>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="C321" s="3"/>
-      <c r="F321" s="3"/>
-      <c r="G321" s="3"/>
-      <c r="H321" s="3"/>
-      <c r="I321" s="3"/>
-      <c r="J321" s="3"/>
-      <c r="K321" s="3"/>
-      <c r="L321" s="6"/>
-      <c r="M321" s="3"/>
-      <c r="N321" s="6"/>
-      <c r="O321" s="3"/>
-      <c r="P321" s="3"/>
-      <c r="Q321" s="3"/>
-      <c r="R321" s="3"/>
-    </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A322" s="2" t="s">
+      <c r="B323" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B322" s="2" t="s">
+      <c r="C323" s="2"/>
+      <c r="F323" s="2"/>
+      <c r="G323" s="2"/>
+      <c r="H323" s="2"/>
+      <c r="I323" s="2"/>
+      <c r="J323" s="2"/>
+      <c r="K323" s="2"/>
+      <c r="L323" s="5"/>
+      <c r="M323" s="2"/>
+      <c r="N323" s="5"/>
+      <c r="O323" s="2"/>
+      <c r="P323" s="2"/>
+      <c r="Q323" s="2"/>
+      <c r="R323" s="2"/>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A324" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="C322" s="2"/>
-      <c r="F322" s="2"/>
-      <c r="G322" s="2"/>
-      <c r="H322" s="2"/>
-      <c r="I322" s="2"/>
-      <c r="J322" s="2"/>
-      <c r="K322" s="2"/>
-      <c r="L322" s="5"/>
-      <c r="M322" s="2"/>
-      <c r="N322" s="5"/>
-      <c r="O322" s="2"/>
-      <c r="P322" s="2"/>
-      <c r="Q322" s="2"/>
-      <c r="R322" s="2"/>
-    </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A323" s="3" t="s">
+      <c r="B324" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="C324" s="3"/>
+      <c r="F324" s="3"/>
+      <c r="G324" s="3"/>
+      <c r="H324" s="3"/>
+      <c r="I324" s="3"/>
+      <c r="J324" s="3"/>
+      <c r="K324" s="3"/>
+      <c r="L324" s="6"/>
+      <c r="M324" s="3"/>
+      <c r="N324" s="6"/>
+      <c r="O324" s="3"/>
+      <c r="P324" s="3"/>
+      <c r="Q324" s="3"/>
+      <c r="R324" s="3"/>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A325" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="C323" s="3"/>
-      <c r="F323" s="3"/>
-      <c r="G323" s="3"/>
-      <c r="H323" s="3"/>
-      <c r="I323" s="3"/>
-      <c r="J323" s="3"/>
-      <c r="K323" s="3"/>
-      <c r="L323" s="6"/>
-      <c r="M323" s="3"/>
-      <c r="N323" s="6"/>
-      <c r="O323" s="3"/>
-      <c r="P323" s="3"/>
-      <c r="Q323" s="3"/>
-      <c r="R323" s="3"/>
-    </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A324" s="2" t="s">
+      <c r="B325" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B324" s="2" t="s">
+      <c r="C325" s="2"/>
+      <c r="F325" s="2"/>
+      <c r="G325" s="2"/>
+      <c r="H325" s="2"/>
+      <c r="I325" s="2"/>
+      <c r="J325" s="2"/>
+      <c r="K325" s="2"/>
+      <c r="L325" s="5"/>
+      <c r="M325" s="2"/>
+      <c r="N325" s="5"/>
+      <c r="O325" s="2"/>
+      <c r="P325" s="2"/>
+      <c r="Q325" s="2"/>
+      <c r="R325" s="2"/>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="C324" s="2"/>
-      <c r="F324" s="2"/>
-      <c r="G324" s="2"/>
-      <c r="H324" s="2"/>
-      <c r="I324" s="2"/>
-      <c r="J324" s="2"/>
-      <c r="K324" s="2"/>
-      <c r="L324" s="5"/>
-      <c r="M324" s="2"/>
-      <c r="N324" s="5"/>
-      <c r="O324" s="2"/>
-      <c r="P324" s="2"/>
-      <c r="Q324" s="2"/>
-      <c r="R324" s="2"/>
-    </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A325" s="3" t="s">
+      <c r="B326" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B325" s="3" t="s">
+      <c r="C326" s="3"/>
+      <c r="F326" s="3"/>
+      <c r="G326" s="3"/>
+      <c r="H326" s="3"/>
+      <c r="I326" s="3"/>
+      <c r="J326" s="3"/>
+      <c r="K326" s="3"/>
+      <c r="L326" s="6"/>
+      <c r="M326" s="3"/>
+      <c r="N326" s="6"/>
+      <c r="O326" s="3"/>
+      <c r="P326" s="3"/>
+      <c r="Q326" s="3"/>
+      <c r="R326" s="3"/>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A327" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C325" s="3"/>
-      <c r="F325" s="3"/>
-      <c r="G325" s="3"/>
-      <c r="H325" s="3"/>
-      <c r="I325" s="3"/>
-      <c r="J325" s="3"/>
-      <c r="K325" s="3"/>
-      <c r="L325" s="6"/>
-      <c r="M325" s="3"/>
-      <c r="N325" s="6"/>
-      <c r="O325" s="3"/>
-      <c r="P325" s="3"/>
-      <c r="Q325" s="3"/>
-      <c r="R325" s="3"/>
-    </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A326" s="2" t="s">
+      <c r="B327" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B326" s="2" t="s">
+      <c r="C327" s="2"/>
+      <c r="F327" s="2"/>
+      <c r="G327" s="2"/>
+      <c r="H327" s="2"/>
+      <c r="I327" s="2"/>
+      <c r="J327" s="2"/>
+      <c r="K327" s="2"/>
+      <c r="L327" s="5"/>
+      <c r="M327" s="2"/>
+      <c r="N327" s="5"/>
+      <c r="O327" s="2"/>
+      <c r="P327" s="2"/>
+      <c r="Q327" s="2"/>
+      <c r="R327" s="2"/>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A328" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="C326" s="2"/>
-      <c r="F326" s="2"/>
-      <c r="G326" s="2"/>
-      <c r="H326" s="2"/>
-      <c r="I326" s="2"/>
-      <c r="J326" s="2"/>
-      <c r="K326" s="2"/>
-      <c r="L326" s="5"/>
-      <c r="M326" s="2"/>
-      <c r="N326" s="5"/>
-      <c r="O326" s="2"/>
-      <c r="P326" s="2"/>
-      <c r="Q326" s="2"/>
-      <c r="R326" s="2"/>
-    </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A327" s="3" t="s">
+      <c r="B328" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B327" s="3" t="s">
+      <c r="C328" s="3"/>
+      <c r="F328" s="3"/>
+      <c r="G328" s="3"/>
+      <c r="H328" s="3"/>
+      <c r="I328" s="3"/>
+      <c r="J328" s="3"/>
+      <c r="K328" s="3"/>
+      <c r="L328" s="6"/>
+      <c r="M328" s="3"/>
+      <c r="N328" s="6"/>
+      <c r="O328" s="3"/>
+      <c r="P328" s="3"/>
+      <c r="Q328" s="3"/>
+      <c r="R328" s="3"/>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A329" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="C327" s="3"/>
-      <c r="F327" s="3"/>
-      <c r="G327" s="3"/>
-      <c r="H327" s="3"/>
-      <c r="I327" s="3"/>
-      <c r="J327" s="3"/>
-      <c r="K327" s="3"/>
-      <c r="L327" s="6"/>
-      <c r="M327" s="3"/>
-      <c r="N327" s="6"/>
-      <c r="O327" s="3"/>
-      <c r="P327" s="3"/>
-      <c r="Q327" s="3"/>
-      <c r="R327" s="3"/>
-    </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A328" s="2" t="s">
+      <c r="B329" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B328" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C328" s="2"/>
-      <c r="F328" s="2"/>
-      <c r="G328" s="2"/>
-      <c r="H328" s="2"/>
-      <c r="I328" s="2"/>
-      <c r="J328" s="2"/>
-      <c r="K328" s="2"/>
-      <c r="L328" s="5"/>
-      <c r="M328" s="2"/>
-      <c r="N328" s="5"/>
-      <c r="O328" s="2"/>
-      <c r="P328" s="2"/>
-      <c r="Q328" s="2"/>
-      <c r="R328" s="2"/>
-    </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A329" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B329" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="C329" s="3"/>
-      <c r="F329" s="3"/>
-      <c r="G329" s="3"/>
-      <c r="H329" s="3"/>
-      <c r="I329" s="3"/>
-      <c r="J329" s="3"/>
-      <c r="K329" s="3"/>
-      <c r="L329" s="6"/>
-      <c r="M329" s="3"/>
-      <c r="N329" s="6"/>
-      <c r="O329" s="3"/>
-      <c r="P329" s="3"/>
-      <c r="Q329" s="3"/>
-      <c r="R329" s="3"/>
+      <c r="C329" s="2"/>
+      <c r="F329" s="2"/>
+      <c r="G329" s="2"/>
+      <c r="H329" s="2"/>
+      <c r="I329" s="2"/>
+      <c r="J329" s="2"/>
+      <c r="K329" s="2"/>
+      <c r="L329" s="5"/>
+      <c r="M329" s="2"/>
+      <c r="N329" s="5"/>
+      <c r="O329" s="2"/>
+      <c r="P329" s="2"/>
+      <c r="Q329" s="2"/>
+      <c r="R329" s="2"/>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A330" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="C330" s="2"/>
-      <c r="F330" s="2"/>
-      <c r="G330" s="2"/>
-      <c r="H330" s="2"/>
-      <c r="I330" s="2"/>
-      <c r="J330" s="2"/>
-      <c r="K330" s="2"/>
-      <c r="L330" s="5"/>
-      <c r="M330" s="2"/>
-      <c r="N330" s="5"/>
-      <c r="O330" s="2"/>
-      <c r="P330" s="2"/>
-      <c r="Q330" s="2"/>
-      <c r="R330" s="2"/>
+      <c r="B330" s="4"/>
+      <c r="C330" s="3"/>
+      <c r="F330" s="3"/>
+      <c r="G330" s="3"/>
+      <c r="H330" s="3"/>
+      <c r="I330" s="3"/>
+      <c r="J330" s="3"/>
+      <c r="K330" s="3"/>
+      <c r="L330" s="6"/>
+      <c r="M330" s="3"/>
+      <c r="N330" s="6"/>
+      <c r="O330" s="3"/>
+      <c r="P330" s="3"/>
+      <c r="Q330" s="3"/>
+      <c r="R330" s="3"/>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B331" s="4"/>
-      <c r="C331" s="3"/>
-      <c r="F331" s="3"/>
-      <c r="G331" s="3"/>
-      <c r="H331" s="3"/>
-      <c r="I331" s="3"/>
-      <c r="J331" s="3"/>
-      <c r="K331" s="3"/>
-      <c r="L331" s="6"/>
-      <c r="M331" s="3"/>
-      <c r="N331" s="6"/>
-      <c r="O331" s="3"/>
-      <c r="P331" s="3"/>
-      <c r="Q331" s="3"/>
-      <c r="R331" s="3"/>
-    </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B332" s="4"/>
-      <c r="C332" s="2"/>
-      <c r="F332" s="2"/>
-      <c r="G332" s="2"/>
-      <c r="H332" s="2"/>
-      <c r="I332" s="2"/>
-      <c r="J332" s="2"/>
-      <c r="K332" s="2"/>
-      <c r="L332" s="5"/>
-      <c r="M332" s="2"/>
-      <c r="N332" s="5"/>
-      <c r="O332" s="2"/>
-      <c r="P332" s="2"/>
-      <c r="Q332" s="2"/>
-      <c r="R332" s="2"/>
+      <c r="C331" s="2"/>
+      <c r="F331" s="2"/>
+      <c r="G331" s="2"/>
+      <c r="H331" s="2"/>
+      <c r="I331" s="2"/>
+      <c r="J331" s="2"/>
+      <c r="K331" s="2"/>
+      <c r="L331" s="5"/>
+      <c r="M331" s="2"/>
+      <c r="N331" s="5"/>
+      <c r="O331" s="2"/>
+      <c r="P331" s="2"/>
+      <c r="Q331" s="2"/>
+      <c r="R331" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dorsa-Co\Desktop\temp\seketala\cache\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA2439C-E691-4D0C-ABC7-FE05FEBB1B03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CBF922-B4E7-436A-B806-78FD705E1D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1380" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="620">
   <si>
     <t>كد</t>
   </si>
@@ -816,12 +816,6 @@
     <t>2800008</t>
   </si>
   <si>
-    <t>2800012</t>
-  </si>
-  <si>
-    <t>2800001</t>
-  </si>
-  <si>
     <t>2800005</t>
   </si>
   <si>
@@ -1650,12 +1644,6 @@
     <t>آب نارنج</t>
   </si>
   <si>
-    <t>آب معدني 1.5 ليتري</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آب معدني </t>
-  </si>
-  <si>
     <t>آب گازدار</t>
   </si>
   <si>
@@ -1729,6 +1717,174 @@
   </si>
   <si>
     <t>سالاد کلم</t>
+  </si>
+  <si>
+    <t>1100065</t>
+  </si>
+  <si>
+    <t>آب معدني 300 سي سي</t>
+  </si>
+  <si>
+    <t>1100067</t>
+  </si>
+  <si>
+    <t>خانواده كوكا با ليوان</t>
+  </si>
+  <si>
+    <t>1100068</t>
+  </si>
+  <si>
+    <t>خانواده فانتا با ليوان</t>
+  </si>
+  <si>
+    <t>1100069</t>
+  </si>
+  <si>
+    <t>خانواده اسپرايت با ليوان</t>
+  </si>
+  <si>
+    <t>1100070</t>
+  </si>
+  <si>
+    <t>خانواده ليموناد فانتا با ليوان</t>
+  </si>
+  <si>
+    <t>1100071</t>
+  </si>
+  <si>
+    <t>خانواده مشكي زيرو با ليوان</t>
+  </si>
+  <si>
+    <t>1100072</t>
+  </si>
+  <si>
+    <t>خانواده شاه توت با ليوان</t>
+  </si>
+  <si>
+    <t>1100073</t>
+  </si>
+  <si>
+    <t>قوطي كوكا با ليوان</t>
+  </si>
+  <si>
+    <t>1100074</t>
+  </si>
+  <si>
+    <t>قوطي فانتا با ليوان</t>
+  </si>
+  <si>
+    <t>1100075</t>
+  </si>
+  <si>
+    <t>قوطي زيرو با ليوان</t>
+  </si>
+  <si>
+    <t>1100076</t>
+  </si>
+  <si>
+    <t>قوطي ليموناد خوشگوار با ليوان</t>
+  </si>
+  <si>
+    <t>1100077</t>
+  </si>
+  <si>
+    <t>قوطي اسپرايت با ليوان</t>
+  </si>
+  <si>
+    <t>1100078</t>
+  </si>
+  <si>
+    <t>هي دي ليمو با ليوان</t>
+  </si>
+  <si>
+    <t>1100079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هي دي هلو با ليوان </t>
+  </si>
+  <si>
+    <t>1100080</t>
+  </si>
+  <si>
+    <t>هي دي استوايي با ليوان</t>
+  </si>
+  <si>
+    <t>1100081</t>
+  </si>
+  <si>
+    <t>هي دي كلاسيك با ليوان</t>
+  </si>
+  <si>
+    <t>1100082</t>
+  </si>
+  <si>
+    <t>هافنبرگ كاكتوس با ليوان</t>
+  </si>
+  <si>
+    <t>1100083</t>
+  </si>
+  <si>
+    <t>دوغ خوشگوار با ليوان</t>
+  </si>
+  <si>
+    <t>هي دي كلاسيك</t>
+  </si>
+  <si>
+    <t>1100056</t>
+  </si>
+  <si>
+    <t>كالاي تست ارزش افزوده</t>
+  </si>
+  <si>
+    <t>1100057</t>
+  </si>
+  <si>
+    <t>بوفالو وينگز فروش</t>
+  </si>
+  <si>
+    <t>1100058</t>
+  </si>
+  <si>
+    <t>سالاد سزار مرغ فروش</t>
+  </si>
+  <si>
+    <t>1100059</t>
+  </si>
+  <si>
+    <t>خوراك فيله سوخاري دو تكه</t>
+  </si>
+  <si>
+    <t>1100060</t>
+  </si>
+  <si>
+    <t>سالاد كلم تكي</t>
+  </si>
+  <si>
+    <t>1100061</t>
+  </si>
+  <si>
+    <t>سس خردل تكي</t>
+  </si>
+  <si>
+    <t>1100062</t>
+  </si>
+  <si>
+    <t>سس فرانسوي تكي</t>
+  </si>
+  <si>
+    <t>1100063</t>
+  </si>
+  <si>
+    <t>خانواده ليمويي</t>
+  </si>
+  <si>
+    <t>1100064</t>
+  </si>
+  <si>
+    <t>خانواده شاتوت</t>
+  </si>
+  <si>
+    <t>آب معدني</t>
   </si>
 </sst>
 </file>
@@ -1754,7 +1910,7 @@
       <name val="Tahoma"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1764,6 +1920,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFECF4FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F1FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1780,11 +1942,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2065,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B288"/>
+  <dimension ref="A1:R331"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
@@ -2077,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -2085,7 +2250,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2093,7 +2258,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2101,7 +2266,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2109,7 +2274,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2117,7 +2282,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2125,7 +2290,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2133,7 +2298,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2141,7 +2306,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2149,7 +2314,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2157,7 +2322,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2165,7 +2330,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2173,7 +2338,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2181,7 +2346,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2189,7 +2354,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2197,7 +2362,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2205,7 +2370,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2213,7 +2378,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2221,7 +2386,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2229,7 +2394,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2237,7 +2402,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2245,7 +2410,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2253,7 +2418,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2261,7 +2426,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2269,7 +2434,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2277,7 +2442,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2285,7 +2450,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2293,7 +2458,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2301,7 +2466,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2309,7 +2474,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2317,7 +2482,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2325,7 +2490,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2333,7 +2498,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2341,7 +2506,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2349,7 +2514,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2357,7 +2522,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2365,7 +2530,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2373,7 +2538,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2381,7 +2546,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2389,7 +2554,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2397,7 +2562,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2405,7 +2570,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2413,7 +2578,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2421,7 +2586,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2429,7 +2594,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2437,7 +2602,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2445,7 +2610,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2453,7 +2618,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2461,7 +2626,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2469,7 +2634,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2477,7 +2642,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2485,7 +2650,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2493,7 +2658,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2501,7 +2666,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2509,7 +2674,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2517,7 +2682,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2525,7 +2690,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2533,7 +2698,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2541,7 +2706,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2549,7 +2714,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2557,7 +2722,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2565,7 +2730,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2573,7 +2738,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2581,7 +2746,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2589,7 +2754,7 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2597,7 +2762,7 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2605,7 +2770,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2613,7 +2778,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2621,7 +2786,7 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2629,7 +2794,7 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2637,7 +2802,7 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2645,7 +2810,7 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2653,7 +2818,7 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2661,7 +2826,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2669,7 +2834,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2677,7 +2842,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2685,7 +2850,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2693,7 +2858,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2701,7 +2866,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2709,7 +2874,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2717,7 +2882,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2725,7 +2890,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2733,7 +2898,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2741,7 +2906,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2749,7 +2914,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2757,7 +2922,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2765,7 +2930,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2773,7 +2938,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2781,7 +2946,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2789,7 +2954,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2797,7 +2962,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2805,7 +2970,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2813,7 +2978,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2821,7 +2986,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -2829,7 +2994,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -2837,7 +3002,7 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2845,7 +3010,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -2853,7 +3018,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -2861,7 +3026,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -2869,7 +3034,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2877,7 +3042,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -2885,7 +3050,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -2893,7 +3058,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -2901,7 +3066,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -2909,7 +3074,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -2917,7 +3082,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -2925,7 +3090,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -2933,7 +3098,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -2941,7 +3106,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -2949,7 +3114,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2957,7 +3122,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2965,7 +3130,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -2973,7 +3138,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -2981,7 +3146,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -2989,7 +3154,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2997,7 +3162,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -3005,7 +3170,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -3013,7 +3178,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -3021,7 +3186,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -3029,7 +3194,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -3037,7 +3202,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -3045,7 +3210,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -3053,7 +3218,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -3061,7 +3226,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -3069,7 +3234,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -3077,7 +3242,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -3085,7 +3250,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -3093,7 +3258,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -3101,7 +3266,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -3109,7 +3274,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -3117,7 +3282,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -3125,7 +3290,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -3133,7 +3298,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -3141,7 +3306,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -3149,7 +3314,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -3157,7 +3322,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -3165,7 +3330,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -3173,7 +3338,7 @@
         <v>137</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -3181,7 +3346,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -3189,7 +3354,7 @@
         <v>139</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -3197,7 +3362,7 @@
         <v>140</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -3205,7 +3370,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -3213,7 +3378,7 @@
         <v>142</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -3221,7 +3386,7 @@
         <v>143</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -3229,7 +3394,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -3237,7 +3402,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -3245,7 +3410,7 @@
         <v>146</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -3253,7 +3418,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -3261,7 +3426,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3269,7 +3434,7 @@
         <v>149</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3277,7 +3442,7 @@
         <v>150</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -3285,7 +3450,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -3293,7 +3458,7 @@
         <v>152</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -3301,7 +3466,7 @@
         <v>153</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -3309,7 +3474,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -3317,7 +3482,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -3325,7 +3490,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -3333,7 +3498,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -3341,7 +3506,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -3349,7 +3514,7 @@
         <v>159</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -3357,7 +3522,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -3365,7 +3530,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -3373,7 +3538,7 @@
         <v>162</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -3381,7 +3546,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -3389,7 +3554,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -3397,7 +3562,7 @@
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -3405,7 +3570,7 @@
         <v>166</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -3413,7 +3578,7 @@
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -3421,7 +3586,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -3429,7 +3594,7 @@
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -3437,7 +3602,7 @@
         <v>170</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -3445,7 +3610,7 @@
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -3453,7 +3618,7 @@
         <v>172</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3461,7 +3626,7 @@
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -3469,7 +3634,7 @@
         <v>174</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -3477,7 +3642,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -3485,7 +3650,7 @@
         <v>176</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3493,7 +3658,7 @@
         <v>177</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -3501,7 +3666,7 @@
         <v>178</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3509,7 +3674,7 @@
         <v>179</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -3517,7 +3682,7 @@
         <v>180</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -3525,7 +3690,7 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3533,7 +3698,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -3541,7 +3706,7 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -3549,7 +3714,7 @@
         <v>184</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -3557,7 +3722,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -3565,7 +3730,7 @@
         <v>186</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -3573,7 +3738,7 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -3581,7 +3746,7 @@
         <v>188</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -3589,7 +3754,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -3597,7 +3762,7 @@
         <v>190</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3605,7 +3770,7 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3613,7 +3778,7 @@
         <v>192</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3621,7 +3786,7 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3629,7 +3794,7 @@
         <v>194</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3637,7 +3802,7 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3645,7 +3810,7 @@
         <v>196</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3653,7 +3818,7 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3661,7 +3826,7 @@
         <v>198</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3669,7 +3834,7 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3677,7 +3842,7 @@
         <v>200</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3685,7 +3850,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3693,7 +3858,7 @@
         <v>202</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3701,7 +3866,7 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3709,7 +3874,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3717,7 +3882,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3725,7 +3890,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3733,7 +3898,7 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -3741,7 +3906,7 @@
         <v>208</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3749,7 +3914,7 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -3757,7 +3922,7 @@
         <v>210</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -3765,7 +3930,7 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -3773,7 +3938,7 @@
         <v>212</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -3781,7 +3946,7 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -3789,7 +3954,7 @@
         <v>214</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -3797,7 +3962,7 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -3805,7 +3970,7 @@
         <v>216</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -3813,7 +3978,7 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -3821,7 +3986,7 @@
         <v>218</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -3829,7 +3994,7 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -3837,7 +4002,7 @@
         <v>220</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -3845,7 +4010,7 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -3853,7 +4018,7 @@
         <v>222</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -3861,7 +4026,7 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -3869,7 +4034,7 @@
         <v>224</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -3877,7 +4042,7 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -3885,7 +4050,7 @@
         <v>226</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -3893,7 +4058,7 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -3901,7 +4066,7 @@
         <v>228</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -3909,7 +4074,7 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -3917,7 +4082,7 @@
         <v>230</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -3925,7 +4090,7 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -3933,7 +4098,7 @@
         <v>232</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -3941,7 +4106,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -3949,7 +4114,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -3957,7 +4122,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -3965,7 +4130,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -3973,7 +4138,7 @@
         <v>237</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -3981,7 +4146,7 @@
         <v>238</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -3989,7 +4154,7 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -3997,7 +4162,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -4005,7 +4170,7 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -4013,7 +4178,7 @@
         <v>242</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -4021,7 +4186,7 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -4029,7 +4194,7 @@
         <v>244</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -4037,7 +4202,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -4045,7 +4210,7 @@
         <v>246</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -4053,7 +4218,7 @@
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -4061,7 +4226,7 @@
         <v>248</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -4069,7 +4234,7 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -4077,7 +4242,7 @@
         <v>250</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -4085,7 +4250,7 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -4093,7 +4258,7 @@
         <v>252</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -4101,7 +4266,7 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -4109,7 +4274,7 @@
         <v>254</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -4117,7 +4282,7 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -4125,7 +4290,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -4133,7 +4298,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -4141,7 +4306,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -4149,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -4157,7 +4322,7 @@
         <v>260</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -4165,7 +4330,7 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -4173,208 +4338,1158 @@
         <v>262</v>
       </c>
       <c r="B263" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A264" s="2">
+        <v>1100066</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A266" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B266" s="3" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A264" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B264" s="2" t="s">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A265" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B265" s="3" t="s">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A268" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B268" s="3" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A266" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B266" s="2" t="s">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A267" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B267" s="3" t="s">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A270" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B270" s="3" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B268" s="2" t="s">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A269" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B269" s="3" t="s">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A272" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B272" s="3" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B270" s="2" t="s">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B273" s="2" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A271" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B271" s="3" t="s">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A274" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B274" s="3" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A272" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B272" s="2" t="s">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A273" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B273" s="3" t="s">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A276" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B276" s="3" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B274" s="2" t="s">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B277" s="2" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A275" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B275" s="3" t="s">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A278" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B278" s="3" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A276" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B276" s="2" t="s">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A279" s="2">
+        <v>2500013</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B280" s="3" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A277" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B277" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A278" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A279" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="B279" s="3" t="s">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A281">
+        <v>1100057</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A280" s="2">
-        <v>2500013</v>
-      </c>
-      <c r="B280" s="2" t="s">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A282">
+        <v>1100059</v>
+      </c>
+      <c r="B282" s="3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A283">
+        <v>1100038</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A284">
+        <v>2100021</v>
+      </c>
+      <c r="B284" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A285">
+        <v>1100062</v>
+      </c>
+      <c r="B285" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A286">
+        <v>1100061</v>
+      </c>
+      <c r="B286" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A281" s="3" t="s">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A287">
+        <v>1100060</v>
+      </c>
+      <c r="B287" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A288" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B288" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C288" s="2"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="2"/>
+      <c r="H288" s="2"/>
+      <c r="I288" s="2"/>
+      <c r="J288" s="2"/>
+      <c r="K288" s="2"/>
+      <c r="L288" s="5"/>
+      <c r="M288" s="2"/>
+      <c r="N288" s="5"/>
+      <c r="O288" s="2"/>
+      <c r="P288" s="2"/>
+      <c r="Q288" s="2"/>
+      <c r="R288" s="2"/>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C289" s="3"/>
+      <c r="F289" s="3"/>
+      <c r="G289" s="3"/>
+      <c r="H289" s="3"/>
+      <c r="I289" s="3"/>
+      <c r="J289" s="3"/>
+      <c r="K289" s="3"/>
+      <c r="L289" s="6"/>
+      <c r="M289" s="3"/>
+      <c r="N289" s="6"/>
+      <c r="O289" s="3"/>
+      <c r="P289" s="3"/>
+      <c r="Q289" s="3"/>
+      <c r="R289" s="3"/>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A290" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C290" s="3"/>
+      <c r="F290" s="3"/>
+      <c r="G290" s="3"/>
+      <c r="H290" s="3"/>
+      <c r="I290" s="3"/>
+      <c r="J290" s="3"/>
+      <c r="K290" s="3"/>
+      <c r="L290" s="6"/>
+      <c r="M290" s="3"/>
+      <c r="N290" s="6"/>
+      <c r="O290" s="3"/>
+      <c r="P290" s="3"/>
+      <c r="Q290" s="3"/>
+      <c r="R290" s="3"/>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="2"/>
+      <c r="H291" s="2"/>
+      <c r="I291" s="2"/>
+      <c r="J291" s="2"/>
+      <c r="K291" s="2"/>
+      <c r="L291" s="5"/>
+      <c r="M291" s="2"/>
+      <c r="N291" s="5"/>
+      <c r="O291" s="2"/>
+      <c r="P291" s="2"/>
+      <c r="Q291" s="2"/>
+      <c r="R291" s="2"/>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A292" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C292" s="3"/>
+      <c r="F292" s="3"/>
+      <c r="G292" s="3"/>
+      <c r="H292" s="3"/>
+      <c r="I292" s="3"/>
+      <c r="J292" s="3"/>
+      <c r="K292" s="3"/>
+      <c r="L292" s="6"/>
+      <c r="M292" s="3"/>
+      <c r="N292" s="6"/>
+      <c r="O292" s="3"/>
+      <c r="P292" s="3"/>
+      <c r="Q292" s="3"/>
+      <c r="R292" s="3"/>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C293" s="2"/>
+      <c r="F293" s="2"/>
+      <c r="G293" s="2"/>
+      <c r="H293" s="2"/>
+      <c r="I293" s="2"/>
+      <c r="J293" s="2"/>
+      <c r="K293" s="2"/>
+      <c r="L293" s="5"/>
+      <c r="M293" s="2"/>
+      <c r="N293" s="5"/>
+      <c r="O293" s="2"/>
+      <c r="P293" s="2"/>
+      <c r="Q293" s="2"/>
+      <c r="R293" s="2"/>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A294" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C294" s="3"/>
+      <c r="F294" s="3"/>
+      <c r="G294" s="3"/>
+      <c r="H294" s="3"/>
+      <c r="I294" s="3"/>
+      <c r="J294" s="3"/>
+      <c r="K294" s="3"/>
+      <c r="L294" s="6"/>
+      <c r="M294" s="3"/>
+      <c r="N294" s="6"/>
+      <c r="O294" s="3"/>
+      <c r="P294" s="3"/>
+      <c r="Q294" s="3"/>
+      <c r="R294" s="3"/>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C295" s="2"/>
+      <c r="F295" s="2"/>
+      <c r="G295" s="2"/>
+      <c r="H295" s="2"/>
+      <c r="I295" s="2"/>
+      <c r="J295" s="2"/>
+      <c r="K295" s="2"/>
+      <c r="L295" s="5"/>
+      <c r="M295" s="2"/>
+      <c r="N295" s="5"/>
+      <c r="O295" s="2"/>
+      <c r="P295" s="2"/>
+      <c r="Q295" s="2"/>
+      <c r="R295" s="2"/>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A296" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C296" s="3"/>
+      <c r="F296" s="3"/>
+      <c r="G296" s="3"/>
+      <c r="H296" s="3"/>
+      <c r="I296" s="3"/>
+      <c r="J296" s="3"/>
+      <c r="K296" s="3"/>
+      <c r="L296" s="6"/>
+      <c r="M296" s="3"/>
+      <c r="N296" s="6"/>
+      <c r="O296" s="3"/>
+      <c r="P296" s="3"/>
+      <c r="Q296" s="3"/>
+      <c r="R296" s="3"/>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C297" s="2"/>
+      <c r="F297" s="2"/>
+      <c r="G297" s="2"/>
+      <c r="H297" s="2"/>
+      <c r="I297" s="2"/>
+      <c r="J297" s="2"/>
+      <c r="K297" s="2"/>
+      <c r="L297" s="5"/>
+      <c r="M297" s="2"/>
+      <c r="N297" s="5"/>
+      <c r="O297" s="2"/>
+      <c r="P297" s="2"/>
+      <c r="Q297" s="2"/>
+      <c r="R297" s="2"/>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A298" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B298" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="B281" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A282">
-        <v>1100057</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A283">
-        <v>1100059</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A284">
-        <v>1100038</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A285">
-        <v>2100021</v>
-      </c>
-      <c r="B285" t="s">
+      <c r="C298" s="3"/>
+      <c r="F298" s="3"/>
+      <c r="G298" s="3"/>
+      <c r="H298" s="3"/>
+      <c r="I298" s="3"/>
+      <c r="J298" s="3"/>
+      <c r="K298" s="3"/>
+      <c r="L298" s="6"/>
+      <c r="M298" s="3"/>
+      <c r="N298" s="6"/>
+      <c r="O298" s="3"/>
+      <c r="P298" s="3"/>
+      <c r="Q298" s="3"/>
+      <c r="R298" s="3"/>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C299" s="2"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
+      <c r="H299" s="2"/>
+      <c r="I299" s="2"/>
+      <c r="J299" s="2"/>
+      <c r="K299" s="2"/>
+      <c r="L299" s="5"/>
+      <c r="M299" s="2"/>
+      <c r="N299" s="5"/>
+      <c r="O299" s="2"/>
+      <c r="P299" s="2"/>
+      <c r="Q299" s="2"/>
+      <c r="R299" s="2"/>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A300" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C300" s="3"/>
+      <c r="F300" s="3"/>
+      <c r="G300" s="3"/>
+      <c r="H300" s="3"/>
+      <c r="I300" s="3"/>
+      <c r="J300" s="3"/>
+      <c r="K300" s="3"/>
+      <c r="L300" s="6"/>
+      <c r="M300" s="3"/>
+      <c r="N300" s="6"/>
+      <c r="O300" s="3"/>
+      <c r="P300" s="3"/>
+      <c r="Q300" s="3"/>
+      <c r="R300" s="3"/>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C301" s="2"/>
+      <c r="F301" s="2"/>
+      <c r="G301" s="2"/>
+      <c r="H301" s="2"/>
+      <c r="I301" s="2"/>
+      <c r="J301" s="2"/>
+      <c r="K301" s="2"/>
+      <c r="L301" s="5"/>
+      <c r="M301" s="2"/>
+      <c r="N301" s="5"/>
+      <c r="O301" s="2"/>
+      <c r="P301" s="2"/>
+      <c r="Q301" s="2"/>
+      <c r="R301" s="2"/>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A302" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C302" s="3"/>
+      <c r="F302" s="3"/>
+      <c r="G302" s="3"/>
+      <c r="H302" s="3"/>
+      <c r="I302" s="3"/>
+      <c r="J302" s="3"/>
+      <c r="K302" s="3"/>
+      <c r="L302" s="6"/>
+      <c r="M302" s="3"/>
+      <c r="N302" s="6"/>
+      <c r="O302" s="3"/>
+      <c r="P302" s="3"/>
+      <c r="Q302" s="3"/>
+      <c r="R302" s="3"/>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C303" s="2"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="2"/>
+      <c r="H303" s="2"/>
+      <c r="I303" s="2"/>
+      <c r="J303" s="2"/>
+      <c r="K303" s="2"/>
+      <c r="L303" s="5"/>
+      <c r="M303" s="2"/>
+      <c r="N303" s="5"/>
+      <c r="O303" s="2"/>
+      <c r="P303" s="2"/>
+      <c r="Q303" s="2"/>
+      <c r="R303" s="2"/>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A304" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C304" s="3"/>
+      <c r="F304" s="3"/>
+      <c r="G304" s="3"/>
+      <c r="H304" s="3"/>
+      <c r="I304" s="3"/>
+      <c r="J304" s="3"/>
+      <c r="K304" s="3"/>
+      <c r="L304" s="6"/>
+      <c r="M304" s="3"/>
+      <c r="N304" s="6"/>
+      <c r="O304" s="3"/>
+      <c r="P304" s="3"/>
+      <c r="Q304" s="3"/>
+      <c r="R304" s="3"/>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C305" s="2"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="2"/>
+      <c r="H305" s="2"/>
+      <c r="I305" s="2"/>
+      <c r="J305" s="2"/>
+      <c r="K305" s="2"/>
+      <c r="L305" s="5"/>
+      <c r="M305" s="2"/>
+      <c r="N305" s="5"/>
+      <c r="O305" s="2"/>
+      <c r="P305" s="2"/>
+      <c r="Q305" s="2"/>
+      <c r="R305" s="2"/>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C306" s="3"/>
+      <c r="F306" s="3"/>
+      <c r="G306" s="3"/>
+      <c r="H306" s="3"/>
+      <c r="I306" s="3"/>
+      <c r="J306" s="3"/>
+      <c r="K306" s="3"/>
+      <c r="L306" s="6"/>
+      <c r="M306" s="3"/>
+      <c r="N306" s="6"/>
+      <c r="O306" s="3"/>
+      <c r="P306" s="3"/>
+      <c r="Q306" s="3"/>
+      <c r="R306" s="3"/>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C307" s="2"/>
+      <c r="F307" s="2"/>
+      <c r="G307" s="2"/>
+      <c r="H307" s="2"/>
+      <c r="I307" s="2"/>
+      <c r="J307" s="2"/>
+      <c r="K307" s="2"/>
+      <c r="L307" s="5"/>
+      <c r="M307" s="2"/>
+      <c r="N307" s="5"/>
+      <c r="O307" s="2"/>
+      <c r="P307" s="2"/>
+      <c r="Q307" s="2"/>
+      <c r="R307" s="2"/>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A308" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C308" s="3"/>
+      <c r="F308" s="3"/>
+      <c r="G308" s="3"/>
+      <c r="H308" s="3"/>
+      <c r="I308" s="3"/>
+      <c r="J308" s="3"/>
+      <c r="K308" s="3"/>
+      <c r="L308" s="6"/>
+      <c r="M308" s="3"/>
+      <c r="N308" s="6"/>
+      <c r="O308" s="3"/>
+      <c r="P308" s="3"/>
+      <c r="Q308" s="3"/>
+      <c r="R308" s="3"/>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A309" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C309" s="2"/>
+      <c r="F309" s="2"/>
+      <c r="G309" s="2"/>
+      <c r="H309" s="2"/>
+      <c r="I309" s="2"/>
+      <c r="J309" s="2"/>
+      <c r="K309" s="2"/>
+      <c r="L309" s="5"/>
+      <c r="M309" s="2"/>
+      <c r="N309" s="5"/>
+      <c r="O309" s="2"/>
+      <c r="P309" s="2"/>
+      <c r="Q309" s="2"/>
+      <c r="R309" s="2"/>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A310" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C310" s="3"/>
+      <c r="F310" s="3"/>
+      <c r="G310" s="3"/>
+      <c r="H310" s="3"/>
+      <c r="I310" s="3"/>
+      <c r="J310" s="3"/>
+      <c r="K310" s="3"/>
+      <c r="L310" s="6"/>
+      <c r="M310" s="3"/>
+      <c r="N310" s="6"/>
+      <c r="O310" s="3"/>
+      <c r="P310" s="3"/>
+      <c r="Q310" s="3"/>
+      <c r="R310" s="3"/>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A311" s="2" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A286">
-        <v>1100062</v>
-      </c>
-      <c r="B286" t="s">
+      <c r="B311" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C311" s="2"/>
+      <c r="F311" s="2"/>
+      <c r="G311" s="2"/>
+      <c r="H311" s="2"/>
+      <c r="I311" s="2"/>
+      <c r="J311" s="2"/>
+      <c r="K311" s="2"/>
+      <c r="L311" s="5"/>
+      <c r="M311" s="2"/>
+      <c r="N311" s="5"/>
+      <c r="O311" s="2"/>
+      <c r="P311" s="2"/>
+      <c r="Q311" s="2"/>
+      <c r="R311" s="2"/>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A312" s="3">
+        <v>1100066</v>
+      </c>
+      <c r="B312" s="3" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A287">
-        <v>1100061</v>
-      </c>
-      <c r="B287" t="s">
+      <c r="C312" s="3"/>
+      <c r="F312" s="3"/>
+      <c r="G312" s="3"/>
+      <c r="H312" s="3"/>
+      <c r="I312" s="3"/>
+      <c r="J312" s="3"/>
+      <c r="K312" s="3"/>
+      <c r="L312" s="6"/>
+      <c r="M312" s="3"/>
+      <c r="N312" s="6"/>
+      <c r="O312" s="3"/>
+      <c r="P312" s="3"/>
+      <c r="Q312" s="3"/>
+      <c r="R312" s="3"/>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A288">
-        <v>1100060</v>
-      </c>
-      <c r="B288" t="s">
+      <c r="B313" s="2" t="s">
         <v>567</v>
       </c>
+      <c r="C313" s="2"/>
+      <c r="F313" s="2"/>
+      <c r="G313" s="2"/>
+      <c r="H313" s="2"/>
+      <c r="I313" s="2"/>
+      <c r="J313" s="2"/>
+      <c r="K313" s="2"/>
+      <c r="L313" s="5"/>
+      <c r="M313" s="2"/>
+      <c r="N313" s="5"/>
+      <c r="O313" s="2"/>
+      <c r="P313" s="2"/>
+      <c r="Q313" s="2"/>
+      <c r="R313" s="2"/>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A314" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="C314" s="3"/>
+      <c r="F314" s="3"/>
+      <c r="G314" s="3"/>
+      <c r="H314" s="3"/>
+      <c r="I314" s="3"/>
+      <c r="J314" s="3"/>
+      <c r="K314" s="3"/>
+      <c r="L314" s="6"/>
+      <c r="M314" s="3"/>
+      <c r="N314" s="6"/>
+      <c r="O314" s="3"/>
+      <c r="P314" s="3"/>
+      <c r="Q314" s="3"/>
+      <c r="R314" s="3"/>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C315" s="2"/>
+      <c r="F315" s="2"/>
+      <c r="G315" s="2"/>
+      <c r="H315" s="2"/>
+      <c r="I315" s="2"/>
+      <c r="J315" s="2"/>
+      <c r="K315" s="2"/>
+      <c r="L315" s="5"/>
+      <c r="M315" s="2"/>
+      <c r="N315" s="5"/>
+      <c r="O315" s="2"/>
+      <c r="P315" s="2"/>
+      <c r="Q315" s="2"/>
+      <c r="R315" s="2"/>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A316" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C316" s="3"/>
+      <c r="F316" s="3"/>
+      <c r="G316" s="3"/>
+      <c r="H316" s="3"/>
+      <c r="I316" s="3"/>
+      <c r="J316" s="3"/>
+      <c r="K316" s="3"/>
+      <c r="L316" s="6"/>
+      <c r="M316" s="3"/>
+      <c r="N316" s="6"/>
+      <c r="O316" s="3"/>
+      <c r="P316" s="3"/>
+      <c r="Q316" s="3"/>
+      <c r="R316" s="3"/>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="C317" s="2"/>
+      <c r="F317" s="2"/>
+      <c r="G317" s="2"/>
+      <c r="H317" s="2"/>
+      <c r="I317" s="2"/>
+      <c r="J317" s="2"/>
+      <c r="K317" s="2"/>
+      <c r="L317" s="5"/>
+      <c r="M317" s="2"/>
+      <c r="N317" s="5"/>
+      <c r="O317" s="2"/>
+      <c r="P317" s="2"/>
+      <c r="Q317" s="2"/>
+      <c r="R317" s="2"/>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A318" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C318" s="3"/>
+      <c r="F318" s="3"/>
+      <c r="G318" s="3"/>
+      <c r="H318" s="3"/>
+      <c r="I318" s="3"/>
+      <c r="J318" s="3"/>
+      <c r="K318" s="3"/>
+      <c r="L318" s="6"/>
+      <c r="M318" s="3"/>
+      <c r="N318" s="6"/>
+      <c r="O318" s="3"/>
+      <c r="P318" s="3"/>
+      <c r="Q318" s="3"/>
+      <c r="R318" s="3"/>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A319" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C319" s="2"/>
+      <c r="F319" s="2"/>
+      <c r="G319" s="2"/>
+      <c r="H319" s="2"/>
+      <c r="I319" s="2"/>
+      <c r="J319" s="2"/>
+      <c r="K319" s="2"/>
+      <c r="L319" s="5"/>
+      <c r="M319" s="2"/>
+      <c r="N319" s="5"/>
+      <c r="O319" s="2"/>
+      <c r="P319" s="2"/>
+      <c r="Q319" s="2"/>
+      <c r="R319" s="2"/>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A320" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="C320" s="3"/>
+      <c r="F320" s="3"/>
+      <c r="G320" s="3"/>
+      <c r="H320" s="3"/>
+      <c r="I320" s="3"/>
+      <c r="J320" s="3"/>
+      <c r="K320" s="3"/>
+      <c r="L320" s="6"/>
+      <c r="M320" s="3"/>
+      <c r="N320" s="6"/>
+      <c r="O320" s="3"/>
+      <c r="P320" s="3"/>
+      <c r="Q320" s="3"/>
+      <c r="R320" s="3"/>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C321" s="2"/>
+      <c r="F321" s="2"/>
+      <c r="G321" s="2"/>
+      <c r="H321" s="2"/>
+      <c r="I321" s="2"/>
+      <c r="J321" s="2"/>
+      <c r="K321" s="2"/>
+      <c r="L321" s="5"/>
+      <c r="M321" s="2"/>
+      <c r="N321" s="5"/>
+      <c r="O321" s="2"/>
+      <c r="P321" s="2"/>
+      <c r="Q321" s="2"/>
+      <c r="R321" s="2"/>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A322" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="C322" s="3"/>
+      <c r="F322" s="3"/>
+      <c r="G322" s="3"/>
+      <c r="H322" s="3"/>
+      <c r="I322" s="3"/>
+      <c r="J322" s="3"/>
+      <c r="K322" s="3"/>
+      <c r="L322" s="6"/>
+      <c r="M322" s="3"/>
+      <c r="N322" s="6"/>
+      <c r="O322" s="3"/>
+      <c r="P322" s="3"/>
+      <c r="Q322" s="3"/>
+      <c r="R322" s="3"/>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C323" s="2"/>
+      <c r="F323" s="2"/>
+      <c r="G323" s="2"/>
+      <c r="H323" s="2"/>
+      <c r="I323" s="2"/>
+      <c r="J323" s="2"/>
+      <c r="K323" s="2"/>
+      <c r="L323" s="5"/>
+      <c r="M323" s="2"/>
+      <c r="N323" s="5"/>
+      <c r="O323" s="2"/>
+      <c r="P323" s="2"/>
+      <c r="Q323" s="2"/>
+      <c r="R323" s="2"/>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A324" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C324" s="3"/>
+      <c r="F324" s="3"/>
+      <c r="G324" s="3"/>
+      <c r="H324" s="3"/>
+      <c r="I324" s="3"/>
+      <c r="J324" s="3"/>
+      <c r="K324" s="3"/>
+      <c r="L324" s="6"/>
+      <c r="M324" s="3"/>
+      <c r="N324" s="6"/>
+      <c r="O324" s="3"/>
+      <c r="P324" s="3"/>
+      <c r="Q324" s="3"/>
+      <c r="R324" s="3"/>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A325" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C325" s="2"/>
+      <c r="F325" s="2"/>
+      <c r="G325" s="2"/>
+      <c r="H325" s="2"/>
+      <c r="I325" s="2"/>
+      <c r="J325" s="2"/>
+      <c r="K325" s="2"/>
+      <c r="L325" s="5"/>
+      <c r="M325" s="2"/>
+      <c r="N325" s="5"/>
+      <c r="O325" s="2"/>
+      <c r="P325" s="2"/>
+      <c r="Q325" s="2"/>
+      <c r="R325" s="2"/>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A326" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C326" s="3"/>
+      <c r="F326" s="3"/>
+      <c r="G326" s="3"/>
+      <c r="H326" s="3"/>
+      <c r="I326" s="3"/>
+      <c r="J326" s="3"/>
+      <c r="K326" s="3"/>
+      <c r="L326" s="6"/>
+      <c r="M326" s="3"/>
+      <c r="N326" s="6"/>
+      <c r="O326" s="3"/>
+      <c r="P326" s="3"/>
+      <c r="Q326" s="3"/>
+      <c r="R326" s="3"/>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A327" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C327" s="2"/>
+      <c r="F327" s="2"/>
+      <c r="G327" s="2"/>
+      <c r="H327" s="2"/>
+      <c r="I327" s="2"/>
+      <c r="J327" s="2"/>
+      <c r="K327" s="2"/>
+      <c r="L327" s="5"/>
+      <c r="M327" s="2"/>
+      <c r="N327" s="5"/>
+      <c r="O327" s="2"/>
+      <c r="P327" s="2"/>
+      <c r="Q327" s="2"/>
+      <c r="R327" s="2"/>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A328" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C328" s="3"/>
+      <c r="F328" s="3"/>
+      <c r="G328" s="3"/>
+      <c r="H328" s="3"/>
+      <c r="I328" s="3"/>
+      <c r="J328" s="3"/>
+      <c r="K328" s="3"/>
+      <c r="L328" s="6"/>
+      <c r="M328" s="3"/>
+      <c r="N328" s="6"/>
+      <c r="O328" s="3"/>
+      <c r="P328" s="3"/>
+      <c r="Q328" s="3"/>
+      <c r="R328" s="3"/>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A329" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C329" s="2"/>
+      <c r="F329" s="2"/>
+      <c r="G329" s="2"/>
+      <c r="H329" s="2"/>
+      <c r="I329" s="2"/>
+      <c r="J329" s="2"/>
+      <c r="K329" s="2"/>
+      <c r="L329" s="5"/>
+      <c r="M329" s="2"/>
+      <c r="N329" s="5"/>
+      <c r="O329" s="2"/>
+      <c r="P329" s="2"/>
+      <c r="Q329" s="2"/>
+      <c r="R329" s="2"/>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B330" s="4"/>
+      <c r="C330" s="3"/>
+      <c r="F330" s="3"/>
+      <c r="G330" s="3"/>
+      <c r="H330" s="3"/>
+      <c r="I330" s="3"/>
+      <c r="J330" s="3"/>
+      <c r="K330" s="3"/>
+      <c r="L330" s="6"/>
+      <c r="M330" s="3"/>
+      <c r="N330" s="6"/>
+      <c r="O330" s="3"/>
+      <c r="P330" s="3"/>
+      <c r="Q330" s="3"/>
+      <c r="R330" s="3"/>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B331" s="4"/>
+      <c r="C331" s="2"/>
+      <c r="F331" s="2"/>
+      <c r="G331" s="2"/>
+      <c r="H331" s="2"/>
+      <c r="I331" s="2"/>
+      <c r="J331" s="2"/>
+      <c r="K331" s="2"/>
+      <c r="L331" s="5"/>
+      <c r="M331" s="2"/>
+      <c r="N331" s="5"/>
+      <c r="O331" s="2"/>
+      <c r="P331" s="2"/>
+      <c r="Q331" s="2"/>
+      <c r="R331" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cache/sepidar_food_code.xlsx
+++ b/cache/sepidar_food_code.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\seketala\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5CBF922-B4E7-436A-B806-78FD705E1D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57359799-3000-414E-A18F-1C97E5676880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="621">
   <si>
     <t>كد</t>
   </si>
@@ -1885,6 +1885,9 @@
   </si>
   <si>
     <t>آب معدني</t>
+  </si>
+  <si>
+    <t>سس سالاد ژامبون و پنير</t>
   </si>
 </sst>
 </file>
@@ -1942,7 +1945,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1950,6 +1953,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2230,11 +2234,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R331"/>
+  <dimension ref="A1:AB726"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -5458,7 +5463,12 @@
       <c r="R329" s="2"/>
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B330" s="4"/>
+      <c r="A330">
+        <v>3000032</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>620</v>
+      </c>
       <c r="C330" s="3"/>
       <c r="F330" s="3"/>
       <c r="G330" s="3"/>
@@ -5491,6 +5501,1554 @@
       <c r="Q331" s="2"/>
       <c r="R331" s="2"/>
     </row>
+    <row r="340" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z340" s="7"/>
+      <c r="AB340" s="7"/>
+    </row>
+    <row r="341" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z341" s="7"/>
+      <c r="AB341" s="7"/>
+    </row>
+    <row r="342" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z342" s="7"/>
+      <c r="AB342" s="7"/>
+    </row>
+    <row r="343" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z343" s="7"/>
+      <c r="AB343" s="7"/>
+    </row>
+    <row r="344" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z344" s="7"/>
+      <c r="AB344" s="7"/>
+    </row>
+    <row r="345" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z345" s="7"/>
+      <c r="AB345" s="7"/>
+    </row>
+    <row r="346" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z346" s="7"/>
+      <c r="AB346" s="7"/>
+    </row>
+    <row r="347" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z347" s="7"/>
+      <c r="AB347" s="7"/>
+    </row>
+    <row r="348" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z348" s="7"/>
+      <c r="AB348" s="7"/>
+    </row>
+    <row r="349" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z349" s="7"/>
+      <c r="AB349" s="7"/>
+    </row>
+    <row r="350" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z350" s="7"/>
+      <c r="AB350" s="7"/>
+    </row>
+    <row r="351" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z351" s="7"/>
+      <c r="AB351" s="7"/>
+    </row>
+    <row r="352" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z352" s="7"/>
+      <c r="AB352" s="7"/>
+    </row>
+    <row r="353" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z353" s="7"/>
+      <c r="AB353" s="7"/>
+    </row>
+    <row r="354" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z354" s="7"/>
+      <c r="AB354" s="7"/>
+    </row>
+    <row r="355" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z355" s="7"/>
+      <c r="AB355" s="7"/>
+    </row>
+    <row r="356" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z356" s="7"/>
+      <c r="AB356" s="7"/>
+    </row>
+    <row r="357" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z357" s="7"/>
+      <c r="AB357" s="7"/>
+    </row>
+    <row r="358" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z358" s="7"/>
+      <c r="AB358" s="7"/>
+    </row>
+    <row r="359" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z359" s="7"/>
+      <c r="AB359" s="7"/>
+    </row>
+    <row r="360" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z360" s="7"/>
+      <c r="AB360" s="7"/>
+    </row>
+    <row r="361" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z361" s="7"/>
+      <c r="AB361" s="7"/>
+    </row>
+    <row r="362" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z362" s="7"/>
+      <c r="AB362" s="7"/>
+    </row>
+    <row r="363" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z363" s="7"/>
+      <c r="AB363" s="7"/>
+    </row>
+    <row r="364" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z364" s="7"/>
+      <c r="AB364" s="7"/>
+    </row>
+    <row r="365" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z365" s="7"/>
+      <c r="AB365" s="7"/>
+    </row>
+    <row r="366" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z366" s="7"/>
+      <c r="AB366" s="7"/>
+    </row>
+    <row r="367" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z367" s="7"/>
+      <c r="AB367" s="7"/>
+    </row>
+    <row r="368" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z368" s="7"/>
+      <c r="AB368" s="7"/>
+    </row>
+    <row r="369" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z369" s="7"/>
+      <c r="AB369" s="7"/>
+    </row>
+    <row r="370" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z370" s="7"/>
+      <c r="AB370" s="7"/>
+    </row>
+    <row r="371" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z371" s="7"/>
+      <c r="AB371" s="7"/>
+    </row>
+    <row r="372" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z372" s="7"/>
+      <c r="AB372" s="7"/>
+    </row>
+    <row r="373" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z373" s="7"/>
+      <c r="AB373" s="7"/>
+    </row>
+    <row r="374" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z374" s="7"/>
+      <c r="AB374" s="7"/>
+    </row>
+    <row r="375" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z375" s="7"/>
+      <c r="AB375" s="7"/>
+    </row>
+    <row r="376" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z376" s="7"/>
+      <c r="AB376" s="7"/>
+    </row>
+    <row r="377" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z377" s="7"/>
+      <c r="AB377" s="7"/>
+    </row>
+    <row r="378" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z378" s="7"/>
+      <c r="AB378" s="7"/>
+    </row>
+    <row r="379" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z379" s="7"/>
+      <c r="AB379" s="7"/>
+    </row>
+    <row r="380" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z380" s="7"/>
+      <c r="AB380" s="7"/>
+    </row>
+    <row r="381" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z381" s="7"/>
+      <c r="AB381" s="7"/>
+    </row>
+    <row r="382" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z382" s="7"/>
+      <c r="AB382" s="7"/>
+    </row>
+    <row r="383" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z383" s="7"/>
+      <c r="AB383" s="7"/>
+    </row>
+    <row r="384" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z384" s="7"/>
+      <c r="AB384" s="7"/>
+    </row>
+    <row r="385" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z385" s="7"/>
+      <c r="AB385" s="7"/>
+    </row>
+    <row r="386" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z386" s="7"/>
+      <c r="AB386" s="7"/>
+    </row>
+    <row r="387" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z387" s="7"/>
+      <c r="AB387" s="7"/>
+    </row>
+    <row r="388" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z388" s="7"/>
+      <c r="AB388" s="7"/>
+    </row>
+    <row r="389" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z389" s="7"/>
+      <c r="AB389" s="7"/>
+    </row>
+    <row r="390" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z390" s="7"/>
+      <c r="AB390" s="7"/>
+    </row>
+    <row r="391" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z391" s="7"/>
+      <c r="AB391" s="7"/>
+    </row>
+    <row r="392" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z392" s="7"/>
+      <c r="AB392" s="7"/>
+    </row>
+    <row r="393" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z393" s="7"/>
+      <c r="AB393" s="7"/>
+    </row>
+    <row r="394" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z394" s="7"/>
+      <c r="AB394" s="7"/>
+    </row>
+    <row r="395" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z395" s="7"/>
+      <c r="AB395" s="7"/>
+    </row>
+    <row r="396" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z396" s="7"/>
+      <c r="AB396" s="7"/>
+    </row>
+    <row r="397" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z397" s="7"/>
+      <c r="AB397" s="7"/>
+    </row>
+    <row r="398" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z398" s="7"/>
+      <c r="AB398" s="7"/>
+    </row>
+    <row r="399" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z399" s="7"/>
+      <c r="AB399" s="7"/>
+    </row>
+    <row r="400" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z400" s="7"/>
+      <c r="AB400" s="7"/>
+    </row>
+    <row r="401" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z401" s="7"/>
+      <c r="AB401" s="7"/>
+    </row>
+    <row r="402" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z402" s="7"/>
+      <c r="AB402" s="7"/>
+    </row>
+    <row r="403" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z403" s="7"/>
+      <c r="AB403" s="7"/>
+    </row>
+    <row r="404" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z404" s="7"/>
+      <c r="AB404" s="7"/>
+    </row>
+    <row r="405" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z405" s="7"/>
+      <c r="AB405" s="7"/>
+    </row>
+    <row r="406" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z406" s="7"/>
+      <c r="AB406" s="7"/>
+    </row>
+    <row r="407" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z407" s="7"/>
+      <c r="AB407" s="7"/>
+    </row>
+    <row r="408" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z408" s="7"/>
+      <c r="AB408" s="7"/>
+    </row>
+    <row r="409" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z409" s="7"/>
+      <c r="AB409" s="7"/>
+    </row>
+    <row r="410" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z410" s="7"/>
+      <c r="AB410" s="7"/>
+    </row>
+    <row r="411" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z411" s="7"/>
+      <c r="AB411" s="7"/>
+    </row>
+    <row r="412" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z412" s="7"/>
+      <c r="AB412" s="7"/>
+    </row>
+    <row r="413" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z413" s="7"/>
+      <c r="AB413" s="7"/>
+    </row>
+    <row r="414" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z414" s="7"/>
+      <c r="AB414" s="7"/>
+    </row>
+    <row r="415" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z415" s="7"/>
+      <c r="AB415" s="7"/>
+    </row>
+    <row r="416" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z416" s="7"/>
+      <c r="AB416" s="7"/>
+    </row>
+    <row r="417" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z417" s="7"/>
+      <c r="AB417" s="7"/>
+    </row>
+    <row r="418" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z418" s="7"/>
+      <c r="AB418" s="7"/>
+    </row>
+    <row r="419" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z419" s="7"/>
+      <c r="AB419" s="7"/>
+    </row>
+    <row r="420" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z420" s="7"/>
+      <c r="AB420" s="7"/>
+    </row>
+    <row r="421" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z421" s="7"/>
+      <c r="AB421" s="7"/>
+    </row>
+    <row r="422" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z422" s="7"/>
+      <c r="AB422" s="7"/>
+    </row>
+    <row r="423" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z423" s="7"/>
+      <c r="AB423" s="7"/>
+    </row>
+    <row r="424" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z424" s="7"/>
+      <c r="AB424" s="7"/>
+    </row>
+    <row r="425" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z425" s="7"/>
+      <c r="AB425" s="7"/>
+    </row>
+    <row r="426" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z426" s="7"/>
+      <c r="AB426" s="7"/>
+    </row>
+    <row r="427" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z427" s="7"/>
+      <c r="AB427" s="7"/>
+    </row>
+    <row r="428" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z428" s="7"/>
+      <c r="AB428" s="7"/>
+    </row>
+    <row r="429" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z429" s="7"/>
+      <c r="AB429" s="7"/>
+    </row>
+    <row r="430" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z430" s="7"/>
+      <c r="AB430" s="7"/>
+    </row>
+    <row r="431" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z431" s="7"/>
+      <c r="AB431" s="7"/>
+    </row>
+    <row r="432" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z432" s="7"/>
+      <c r="AB432" s="7"/>
+    </row>
+    <row r="433" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z433" s="7"/>
+      <c r="AB433" s="7"/>
+    </row>
+    <row r="434" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z434" s="7"/>
+      <c r="AB434" s="7"/>
+    </row>
+    <row r="435" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z435" s="7"/>
+      <c r="AB435" s="7"/>
+    </row>
+    <row r="436" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z436" s="7"/>
+      <c r="AB436" s="7"/>
+    </row>
+    <row r="437" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z437" s="7"/>
+      <c r="AB437" s="7"/>
+    </row>
+    <row r="438" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z438" s="7"/>
+      <c r="AB438" s="7"/>
+    </row>
+    <row r="439" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z439" s="7"/>
+      <c r="AB439" s="7"/>
+    </row>
+    <row r="440" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z440" s="7"/>
+      <c r="AB440" s="7"/>
+    </row>
+    <row r="441" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z441" s="7"/>
+      <c r="AB441" s="7"/>
+    </row>
+    <row r="442" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z442" s="7"/>
+      <c r="AB442" s="7"/>
+    </row>
+    <row r="443" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z443" s="7"/>
+      <c r="AB443" s="7"/>
+    </row>
+    <row r="444" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z444" s="7"/>
+      <c r="AB444" s="7"/>
+    </row>
+    <row r="445" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z445" s="7"/>
+      <c r="AB445" s="7"/>
+    </row>
+    <row r="446" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z446" s="7"/>
+      <c r="AB446" s="7"/>
+    </row>
+    <row r="447" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z447" s="7"/>
+      <c r="AB447" s="7"/>
+    </row>
+    <row r="448" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z448" s="7"/>
+      <c r="AB448" s="7"/>
+    </row>
+    <row r="449" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z449" s="7"/>
+      <c r="AB449" s="7"/>
+    </row>
+    <row r="450" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z450" s="7"/>
+      <c r="AB450" s="7"/>
+    </row>
+    <row r="451" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z451" s="7"/>
+      <c r="AB451" s="7"/>
+    </row>
+    <row r="452" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z452" s="7"/>
+      <c r="AB452" s="7"/>
+    </row>
+    <row r="453" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z453" s="7"/>
+      <c r="AB453" s="7"/>
+    </row>
+    <row r="454" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z454" s="7"/>
+      <c r="AB454" s="7"/>
+    </row>
+    <row r="455" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z455" s="7"/>
+      <c r="AB455" s="7"/>
+    </row>
+    <row r="456" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z456" s="7"/>
+      <c r="AB456" s="7"/>
+    </row>
+    <row r="457" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z457" s="7"/>
+      <c r="AB457" s="7"/>
+    </row>
+    <row r="458" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z458" s="7"/>
+      <c r="AB458" s="7"/>
+    </row>
+    <row r="459" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z459" s="7"/>
+      <c r="AB459" s="7"/>
+    </row>
+    <row r="460" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z460" s="7"/>
+      <c r="AB460" s="7"/>
+    </row>
+    <row r="461" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z461" s="7"/>
+      <c r="AB461" s="7"/>
+    </row>
+    <row r="462" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z462" s="7"/>
+      <c r="AB462" s="7"/>
+    </row>
+    <row r="463" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z463" s="7"/>
+      <c r="AB463" s="7"/>
+    </row>
+    <row r="464" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z464" s="7"/>
+      <c r="AB464" s="7"/>
+    </row>
+    <row r="465" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z465" s="7"/>
+      <c r="AB465" s="7"/>
+    </row>
+    <row r="466" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z466" s="7"/>
+      <c r="AB466" s="7"/>
+    </row>
+    <row r="467" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z467" s="7"/>
+      <c r="AB467" s="7"/>
+    </row>
+    <row r="468" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z468" s="7"/>
+      <c r="AB468" s="7"/>
+    </row>
+    <row r="469" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z469" s="7"/>
+      <c r="AB469" s="7"/>
+    </row>
+    <row r="470" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z470" s="7"/>
+      <c r="AB470" s="7"/>
+    </row>
+    <row r="471" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z471" s="7"/>
+      <c r="AB471" s="7"/>
+    </row>
+    <row r="472" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z472" s="7"/>
+      <c r="AB472" s="7"/>
+    </row>
+    <row r="473" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z473" s="7"/>
+      <c r="AB473" s="7"/>
+    </row>
+    <row r="474" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z474" s="7"/>
+      <c r="AB474" s="7"/>
+    </row>
+    <row r="475" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z475" s="7"/>
+      <c r="AB475" s="7"/>
+    </row>
+    <row r="476" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z476" s="7"/>
+      <c r="AB476" s="7"/>
+    </row>
+    <row r="477" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z477" s="7"/>
+      <c r="AB477" s="7"/>
+    </row>
+    <row r="478" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z478" s="7"/>
+      <c r="AB478" s="7"/>
+    </row>
+    <row r="479" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z479" s="7"/>
+      <c r="AB479" s="7"/>
+    </row>
+    <row r="480" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z480" s="7"/>
+      <c r="AB480" s="7"/>
+    </row>
+    <row r="481" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z481" s="7"/>
+      <c r="AB481" s="7"/>
+    </row>
+    <row r="482" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z482" s="7"/>
+      <c r="AB482" s="7"/>
+    </row>
+    <row r="483" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z483" s="7"/>
+      <c r="AB483" s="7"/>
+    </row>
+    <row r="484" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z484" s="7"/>
+      <c r="AB484" s="7"/>
+    </row>
+    <row r="485" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z485" s="7"/>
+      <c r="AB485" s="7"/>
+    </row>
+    <row r="486" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z486" s="7"/>
+      <c r="AB486" s="7"/>
+    </row>
+    <row r="487" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z487" s="7"/>
+      <c r="AB487" s="7"/>
+    </row>
+    <row r="488" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z488" s="7"/>
+      <c r="AB488" s="7"/>
+    </row>
+    <row r="489" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z489" s="7"/>
+      <c r="AB489" s="7"/>
+    </row>
+    <row r="490" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z490" s="7"/>
+      <c r="AB490" s="7"/>
+    </row>
+    <row r="491" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z491" s="7"/>
+      <c r="AB491" s="7"/>
+    </row>
+    <row r="492" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z492" s="7"/>
+      <c r="AB492" s="7"/>
+    </row>
+    <row r="493" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z493" s="7"/>
+      <c r="AB493" s="7"/>
+    </row>
+    <row r="494" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z494" s="7"/>
+      <c r="AB494" s="7"/>
+    </row>
+    <row r="495" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z495" s="7"/>
+      <c r="AB495" s="7"/>
+    </row>
+    <row r="496" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z496" s="7"/>
+      <c r="AB496" s="7"/>
+    </row>
+    <row r="497" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z497" s="7"/>
+      <c r="AB497" s="7"/>
+    </row>
+    <row r="498" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z498" s="7"/>
+      <c r="AB498" s="7"/>
+    </row>
+    <row r="499" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z499" s="7"/>
+      <c r="AB499" s="7"/>
+    </row>
+    <row r="500" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z500" s="7"/>
+      <c r="AB500" s="7"/>
+    </row>
+    <row r="501" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z501" s="7"/>
+      <c r="AB501" s="7"/>
+    </row>
+    <row r="502" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z502" s="7"/>
+      <c r="AB502" s="7"/>
+    </row>
+    <row r="503" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z503" s="7"/>
+      <c r="AB503" s="7"/>
+    </row>
+    <row r="504" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z504" s="7"/>
+      <c r="AB504" s="7"/>
+    </row>
+    <row r="505" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z505" s="7"/>
+      <c r="AB505" s="7"/>
+    </row>
+    <row r="506" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z506" s="7"/>
+      <c r="AB506" s="7"/>
+    </row>
+    <row r="507" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z507" s="7"/>
+      <c r="AB507" s="7"/>
+    </row>
+    <row r="508" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z508" s="7"/>
+      <c r="AB508" s="7"/>
+    </row>
+    <row r="509" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z509" s="7"/>
+      <c r="AB509" s="7"/>
+    </row>
+    <row r="510" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z510" s="7"/>
+      <c r="AB510" s="7"/>
+    </row>
+    <row r="511" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z511" s="7"/>
+      <c r="AB511" s="7"/>
+    </row>
+    <row r="512" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z512" s="7"/>
+      <c r="AB512" s="7"/>
+    </row>
+    <row r="513" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z513" s="7"/>
+      <c r="AB513" s="7"/>
+    </row>
+    <row r="514" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z514" s="7"/>
+      <c r="AB514" s="7"/>
+    </row>
+    <row r="515" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z515" s="7"/>
+      <c r="AB515" s="7"/>
+    </row>
+    <row r="516" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z516" s="7"/>
+      <c r="AB516" s="7"/>
+    </row>
+    <row r="517" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z517" s="7"/>
+      <c r="AB517" s="7"/>
+    </row>
+    <row r="518" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z518" s="7"/>
+      <c r="AB518" s="7"/>
+    </row>
+    <row r="519" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z519" s="7"/>
+      <c r="AB519" s="7"/>
+    </row>
+    <row r="520" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z520" s="7"/>
+      <c r="AB520" s="7"/>
+    </row>
+    <row r="521" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z521" s="7"/>
+      <c r="AB521" s="7"/>
+    </row>
+    <row r="522" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z522" s="7"/>
+      <c r="AB522" s="7"/>
+    </row>
+    <row r="523" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z523" s="7"/>
+      <c r="AB523" s="7"/>
+    </row>
+    <row r="524" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z524" s="7"/>
+      <c r="AB524" s="7"/>
+    </row>
+    <row r="525" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z525" s="7"/>
+      <c r="AB525" s="7"/>
+    </row>
+    <row r="526" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z526" s="7"/>
+      <c r="AB526" s="7"/>
+    </row>
+    <row r="527" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z527" s="7"/>
+      <c r="AB527" s="7"/>
+    </row>
+    <row r="528" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z528" s="7"/>
+      <c r="AB528" s="7"/>
+    </row>
+    <row r="529" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z529" s="7"/>
+      <c r="AB529" s="7"/>
+    </row>
+    <row r="530" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z530" s="7"/>
+      <c r="AB530" s="7"/>
+    </row>
+    <row r="531" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z531" s="7"/>
+      <c r="AB531" s="7"/>
+    </row>
+    <row r="532" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z532" s="7"/>
+      <c r="AB532" s="7"/>
+    </row>
+    <row r="533" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z533" s="7"/>
+      <c r="AB533" s="7"/>
+    </row>
+    <row r="534" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z534" s="7"/>
+      <c r="AB534" s="7"/>
+    </row>
+    <row r="535" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z535" s="7"/>
+      <c r="AB535" s="7"/>
+    </row>
+    <row r="536" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z536" s="7"/>
+      <c r="AB536" s="7"/>
+    </row>
+    <row r="537" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z537" s="7"/>
+      <c r="AB537" s="7"/>
+    </row>
+    <row r="538" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z538" s="7"/>
+      <c r="AB538" s="7"/>
+    </row>
+    <row r="539" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z539" s="7"/>
+      <c r="AB539" s="7"/>
+    </row>
+    <row r="540" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z540" s="7"/>
+      <c r="AB540" s="7"/>
+    </row>
+    <row r="541" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z541" s="7"/>
+      <c r="AB541" s="7"/>
+    </row>
+    <row r="542" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z542" s="7"/>
+      <c r="AB542" s="7"/>
+    </row>
+    <row r="543" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z543" s="7"/>
+      <c r="AB543" s="7"/>
+    </row>
+    <row r="544" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z544" s="7"/>
+      <c r="AB544" s="7"/>
+    </row>
+    <row r="545" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z545" s="7"/>
+      <c r="AB545" s="7"/>
+    </row>
+    <row r="546" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z546" s="7"/>
+      <c r="AB546" s="7"/>
+    </row>
+    <row r="547" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z547" s="7"/>
+      <c r="AB547" s="7"/>
+    </row>
+    <row r="548" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z548" s="7"/>
+      <c r="AB548" s="7"/>
+    </row>
+    <row r="549" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z549" s="7"/>
+      <c r="AB549" s="7"/>
+    </row>
+    <row r="550" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z550" s="7"/>
+      <c r="AB550" s="7"/>
+    </row>
+    <row r="551" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z551" s="7"/>
+      <c r="AB551" s="7"/>
+    </row>
+    <row r="552" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z552" s="7"/>
+      <c r="AB552" s="7"/>
+    </row>
+    <row r="553" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z553" s="7"/>
+      <c r="AB553" s="7"/>
+    </row>
+    <row r="554" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z554" s="7"/>
+      <c r="AB554" s="7"/>
+    </row>
+    <row r="555" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z555" s="7"/>
+      <c r="AB555" s="7"/>
+    </row>
+    <row r="556" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z556" s="7"/>
+      <c r="AB556" s="7"/>
+    </row>
+    <row r="557" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z557" s="7"/>
+      <c r="AB557" s="7"/>
+    </row>
+    <row r="558" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z558" s="7"/>
+      <c r="AB558" s="7"/>
+    </row>
+    <row r="559" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z559" s="7"/>
+      <c r="AB559" s="7"/>
+    </row>
+    <row r="560" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z560" s="7"/>
+      <c r="AB560" s="7"/>
+    </row>
+    <row r="561" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z561" s="7"/>
+      <c r="AB561" s="7"/>
+    </row>
+    <row r="562" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z562" s="7"/>
+      <c r="AB562" s="7"/>
+    </row>
+    <row r="563" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z563" s="7"/>
+      <c r="AB563" s="7"/>
+    </row>
+    <row r="564" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z564" s="7"/>
+      <c r="AB564" s="7"/>
+    </row>
+    <row r="565" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z565" s="7"/>
+      <c r="AB565" s="7"/>
+    </row>
+    <row r="566" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z566" s="7"/>
+      <c r="AB566" s="7"/>
+    </row>
+    <row r="567" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z567" s="7"/>
+      <c r="AB567" s="7"/>
+    </row>
+    <row r="568" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z568" s="7"/>
+      <c r="AB568" s="7"/>
+    </row>
+    <row r="569" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z569" s="7"/>
+      <c r="AB569" s="7"/>
+    </row>
+    <row r="570" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z570" s="7"/>
+      <c r="AB570" s="7"/>
+    </row>
+    <row r="571" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z571" s="7"/>
+      <c r="AB571" s="7"/>
+    </row>
+    <row r="572" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z572" s="7"/>
+      <c r="AB572" s="7"/>
+    </row>
+    <row r="573" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z573" s="7"/>
+      <c r="AB573" s="7"/>
+    </row>
+    <row r="574" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z574" s="7"/>
+      <c r="AB574" s="7"/>
+    </row>
+    <row r="575" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z575" s="7"/>
+      <c r="AB575" s="7"/>
+    </row>
+    <row r="576" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z576" s="7"/>
+      <c r="AB576" s="7"/>
+    </row>
+    <row r="577" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z577" s="7"/>
+      <c r="AB577" s="7"/>
+    </row>
+    <row r="578" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z578" s="7"/>
+      <c r="AB578" s="7"/>
+    </row>
+    <row r="579" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z579" s="7"/>
+      <c r="AB579" s="7"/>
+    </row>
+    <row r="580" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z580" s="7"/>
+      <c r="AB580" s="7"/>
+    </row>
+    <row r="581" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z581" s="7"/>
+      <c r="AB581" s="7"/>
+    </row>
+    <row r="582" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z582" s="7"/>
+      <c r="AB582" s="7"/>
+    </row>
+    <row r="583" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z583" s="7"/>
+      <c r="AB583" s="7"/>
+    </row>
+    <row r="584" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z584" s="7"/>
+      <c r="AB584" s="7"/>
+    </row>
+    <row r="585" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z585" s="7"/>
+      <c r="AB585" s="7"/>
+    </row>
+    <row r="586" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z586" s="7"/>
+      <c r="AB586" s="7"/>
+    </row>
+    <row r="587" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z587" s="7"/>
+      <c r="AB587" s="7"/>
+    </row>
+    <row r="588" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z588" s="7"/>
+      <c r="AB588" s="7"/>
+    </row>
+    <row r="589" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z589" s="7"/>
+      <c r="AB589" s="7"/>
+    </row>
+    <row r="590" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z590" s="7"/>
+      <c r="AB590" s="7"/>
+    </row>
+    <row r="591" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z591" s="7"/>
+      <c r="AB591" s="7"/>
+    </row>
+    <row r="592" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z592" s="7"/>
+      <c r="AB592" s="7"/>
+    </row>
+    <row r="593" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z593" s="7"/>
+      <c r="AB593" s="7"/>
+    </row>
+    <row r="594" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z594" s="7"/>
+      <c r="AB594" s="7"/>
+    </row>
+    <row r="595" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z595" s="7"/>
+      <c r="AB595" s="7"/>
+    </row>
+    <row r="596" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z596" s="7"/>
+      <c r="AB596" s="7"/>
+    </row>
+    <row r="597" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z597" s="7"/>
+      <c r="AB597" s="7"/>
+    </row>
+    <row r="598" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z598" s="7"/>
+      <c r="AB598" s="7"/>
+    </row>
+    <row r="599" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z599" s="7"/>
+      <c r="AB599" s="7"/>
+    </row>
+    <row r="600" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z600" s="7"/>
+      <c r="AB600" s="7"/>
+    </row>
+    <row r="601" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z601" s="7"/>
+      <c r="AB601" s="7"/>
+    </row>
+    <row r="602" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z602" s="7"/>
+      <c r="AB602" s="7"/>
+    </row>
+    <row r="603" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z603" s="7"/>
+      <c r="AB603" s="7"/>
+    </row>
+    <row r="604" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z604" s="7"/>
+      <c r="AB604" s="7"/>
+    </row>
+    <row r="605" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z605" s="7"/>
+      <c r="AB605" s="7"/>
+    </row>
+    <row r="606" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z606" s="7"/>
+      <c r="AB606" s="7"/>
+    </row>
+    <row r="607" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z607" s="7"/>
+      <c r="AB607" s="7"/>
+    </row>
+    <row r="608" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z608" s="7"/>
+      <c r="AB608" s="7"/>
+    </row>
+    <row r="609" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z609" s="7"/>
+      <c r="AB609" s="7"/>
+    </row>
+    <row r="610" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z610" s="7"/>
+      <c r="AB610" s="7"/>
+    </row>
+    <row r="611" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z611" s="7"/>
+      <c r="AB611" s="7"/>
+    </row>
+    <row r="612" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z612" s="7"/>
+      <c r="AB612" s="7"/>
+    </row>
+    <row r="613" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z613" s="7"/>
+      <c r="AB613" s="7"/>
+    </row>
+    <row r="614" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z614" s="7"/>
+      <c r="AB614" s="7"/>
+    </row>
+    <row r="615" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z615" s="7"/>
+      <c r="AB615" s="7"/>
+    </row>
+    <row r="616" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z616" s="7"/>
+      <c r="AB616" s="7"/>
+    </row>
+    <row r="617" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z617" s="7"/>
+      <c r="AB617" s="7"/>
+    </row>
+    <row r="618" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z618" s="7"/>
+      <c r="AB618" s="7"/>
+    </row>
+    <row r="619" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z619" s="7"/>
+      <c r="AB619" s="7"/>
+    </row>
+    <row r="620" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z620" s="7"/>
+      <c r="AB620" s="7"/>
+    </row>
+    <row r="621" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z621" s="7"/>
+      <c r="AB621" s="7"/>
+    </row>
+    <row r="622" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z622" s="7"/>
+      <c r="AB622" s="7"/>
+    </row>
+    <row r="623" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z623" s="7"/>
+      <c r="AB623" s="7"/>
+    </row>
+    <row r="624" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z624" s="7"/>
+      <c r="AB624" s="7"/>
+    </row>
+    <row r="625" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z625" s="7"/>
+      <c r="AB625" s="7"/>
+    </row>
+    <row r="626" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z626" s="7"/>
+      <c r="AB626" s="7"/>
+    </row>
+    <row r="627" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z627" s="7"/>
+      <c r="AB627" s="7"/>
+    </row>
+    <row r="628" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z628" s="7"/>
+      <c r="AB628" s="7"/>
+    </row>
+    <row r="629" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z629" s="7"/>
+      <c r="AB629" s="7"/>
+    </row>
+    <row r="630" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z630" s="7"/>
+      <c r="AB630" s="7"/>
+    </row>
+    <row r="631" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z631" s="7"/>
+      <c r="AB631" s="7"/>
+    </row>
+    <row r="632" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z632" s="7"/>
+      <c r="AB632" s="7"/>
+    </row>
+    <row r="633" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z633" s="7"/>
+      <c r="AB633" s="7"/>
+    </row>
+    <row r="634" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z634" s="7"/>
+      <c r="AB634" s="7"/>
+    </row>
+    <row r="635" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z635" s="7"/>
+      <c r="AB635" s="7"/>
+    </row>
+    <row r="636" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z636" s="7"/>
+      <c r="AB636" s="7"/>
+    </row>
+    <row r="637" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z637" s="7"/>
+      <c r="AB637" s="7"/>
+    </row>
+    <row r="638" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z638" s="7"/>
+      <c r="AB638" s="7"/>
+    </row>
+    <row r="639" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z639" s="7"/>
+      <c r="AB639" s="7"/>
+    </row>
+    <row r="640" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z640" s="7"/>
+      <c r="AB640" s="7"/>
+    </row>
+    <row r="641" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z641" s="7"/>
+      <c r="AB641" s="7"/>
+    </row>
+    <row r="642" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z642" s="7"/>
+      <c r="AB642" s="7"/>
+    </row>
+    <row r="643" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z643" s="7"/>
+      <c r="AB643" s="7"/>
+    </row>
+    <row r="644" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z644" s="7"/>
+      <c r="AB644" s="7"/>
+    </row>
+    <row r="645" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z645" s="7"/>
+      <c r="AB645" s="7"/>
+    </row>
+    <row r="646" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z646" s="7"/>
+      <c r="AB646" s="7"/>
+    </row>
+    <row r="647" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z647" s="7"/>
+      <c r="AB647" s="7"/>
+    </row>
+    <row r="648" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z648" s="7"/>
+      <c r="AB648" s="7"/>
+    </row>
+    <row r="649" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z649" s="7"/>
+      <c r="AB649" s="7"/>
+    </row>
+    <row r="650" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z650" s="7"/>
+      <c r="AB650" s="7"/>
+    </row>
+    <row r="651" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z651" s="7"/>
+      <c r="AB651" s="7"/>
+    </row>
+    <row r="652" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z652" s="7"/>
+      <c r="AB652" s="7"/>
+    </row>
+    <row r="653" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z653" s="7"/>
+      <c r="AB653" s="7"/>
+    </row>
+    <row r="654" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z654" s="7"/>
+      <c r="AB654" s="7"/>
+    </row>
+    <row r="655" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z655" s="7"/>
+      <c r="AB655" s="7"/>
+    </row>
+    <row r="656" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z656" s="7"/>
+      <c r="AB656" s="7"/>
+    </row>
+    <row r="657" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z657" s="7"/>
+      <c r="AB657" s="7"/>
+    </row>
+    <row r="658" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z658" s="7"/>
+      <c r="AB658" s="7"/>
+    </row>
+    <row r="659" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z659" s="7"/>
+      <c r="AB659" s="7"/>
+    </row>
+    <row r="660" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z660" s="7"/>
+      <c r="AB660" s="7"/>
+    </row>
+    <row r="661" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z661" s="7"/>
+      <c r="AB661" s="7"/>
+    </row>
+    <row r="662" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z662" s="7"/>
+      <c r="AB662" s="7"/>
+    </row>
+    <row r="663" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z663" s="7"/>
+      <c r="AB663" s="7"/>
+    </row>
+    <row r="664" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z664" s="7"/>
+      <c r="AB664" s="7"/>
+    </row>
+    <row r="665" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z665" s="7"/>
+      <c r="AB665" s="7"/>
+    </row>
+    <row r="666" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z666" s="7"/>
+      <c r="AB666" s="7"/>
+    </row>
+    <row r="667" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z667" s="7"/>
+      <c r="AB667" s="7"/>
+    </row>
+    <row r="668" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z668" s="7"/>
+      <c r="AB668" s="7"/>
+    </row>
+    <row r="669" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z669" s="7"/>
+      <c r="AB669" s="7"/>
+    </row>
+    <row r="670" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z670" s="7"/>
+      <c r="AB670" s="7"/>
+    </row>
+    <row r="671" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z671" s="7"/>
+      <c r="AB671" s="7"/>
+    </row>
+    <row r="672" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z672" s="7"/>
+      <c r="AB672" s="7"/>
+    </row>
+    <row r="673" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z673" s="7"/>
+      <c r="AB673" s="7"/>
+    </row>
+    <row r="674" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z674" s="7"/>
+      <c r="AB674" s="7"/>
+    </row>
+    <row r="675" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z675" s="7"/>
+      <c r="AB675" s="7"/>
+    </row>
+    <row r="676" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z676" s="7"/>
+      <c r="AB676" s="7"/>
+    </row>
+    <row r="677" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z677" s="7"/>
+      <c r="AB677" s="7"/>
+    </row>
+    <row r="678" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z678" s="7"/>
+      <c r="AB678" s="7"/>
+    </row>
+    <row r="679" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z679" s="7"/>
+      <c r="AB679" s="7"/>
+    </row>
+    <row r="680" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z680" s="7"/>
+      <c r="AB680" s="7"/>
+    </row>
+    <row r="681" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z681" s="7"/>
+      <c r="AB681" s="7"/>
+    </row>
+    <row r="682" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z682" s="7"/>
+      <c r="AB682" s="7"/>
+    </row>
+    <row r="683" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z683" s="7"/>
+      <c r="AB683" s="7"/>
+    </row>
+    <row r="684" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z684" s="7"/>
+      <c r="AB684" s="7"/>
+    </row>
+    <row r="685" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z685" s="7"/>
+      <c r="AB685" s="7"/>
+    </row>
+    <row r="686" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z686" s="7"/>
+      <c r="AB686" s="7"/>
+    </row>
+    <row r="687" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z687" s="7"/>
+      <c r="AB687" s="7"/>
+    </row>
+    <row r="688" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z688" s="7"/>
+      <c r="AB688" s="7"/>
+    </row>
+    <row r="689" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z689" s="7"/>
+      <c r="AB689" s="7"/>
+    </row>
+    <row r="690" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z690" s="7"/>
+      <c r="AB690" s="7"/>
+    </row>
+    <row r="691" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z691" s="7"/>
+      <c r="AB691" s="7"/>
+    </row>
+    <row r="692" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z692" s="7"/>
+      <c r="AB692" s="7"/>
+    </row>
+    <row r="693" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z693" s="7"/>
+      <c r="AB693" s="7"/>
+    </row>
+    <row r="694" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z694" s="7"/>
+      <c r="AB694" s="7"/>
+    </row>
+    <row r="695" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z695" s="7"/>
+      <c r="AB695" s="7"/>
+    </row>
+    <row r="696" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z696" s="7"/>
+      <c r="AB696" s="7"/>
+    </row>
+    <row r="697" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z697" s="7"/>
+      <c r="AB697" s="7"/>
+    </row>
+    <row r="698" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z698" s="7"/>
+      <c r="AB698" s="7"/>
+    </row>
+    <row r="699" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z699" s="7"/>
+      <c r="AB699" s="7"/>
+    </row>
+    <row r="700" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z700" s="7"/>
+      <c r="AB700" s="7"/>
+    </row>
+    <row r="701" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z701" s="7"/>
+      <c r="AB701" s="7"/>
+    </row>
+    <row r="702" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z702" s="7"/>
+      <c r="AB702" s="7"/>
+    </row>
+    <row r="703" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z703" s="7"/>
+      <c r="AB703" s="7"/>
+    </row>
+    <row r="704" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z704" s="7"/>
+      <c r="AB704" s="7"/>
+    </row>
+    <row r="705" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z705" s="7"/>
+      <c r="AB705" s="7"/>
+    </row>
+    <row r="706" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z706" s="7"/>
+      <c r="AB706" s="7"/>
+    </row>
+    <row r="707" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z707" s="7"/>
+      <c r="AB707" s="7"/>
+    </row>
+    <row r="708" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z708" s="7"/>
+      <c r="AB708" s="7"/>
+    </row>
+    <row r="709" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z709" s="7"/>
+      <c r="AB709" s="7"/>
+    </row>
+    <row r="710" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z710" s="7"/>
+      <c r="AB710" s="7"/>
+    </row>
+    <row r="711" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z711" s="7"/>
+      <c r="AB711" s="7"/>
+    </row>
+    <row r="712" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z712" s="7"/>
+      <c r="AB712" s="7"/>
+    </row>
+    <row r="713" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z713" s="7"/>
+      <c r="AB713" s="7"/>
+    </row>
+    <row r="714" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z714" s="7"/>
+      <c r="AB714" s="7"/>
+    </row>
+    <row r="715" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z715" s="7"/>
+      <c r="AB715" s="7"/>
+    </row>
+    <row r="716" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z716" s="7"/>
+      <c r="AB716" s="7"/>
+    </row>
+    <row r="717" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z717" s="7"/>
+      <c r="AB717" s="7"/>
+    </row>
+    <row r="718" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z718" s="7"/>
+      <c r="AB718" s="7"/>
+    </row>
+    <row r="719" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z719" s="7"/>
+      <c r="AB719" s="7"/>
+    </row>
+    <row r="720" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z720" s="7"/>
+      <c r="AB720" s="7"/>
+    </row>
+    <row r="721" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z721" s="7"/>
+      <c r="AB721" s="7"/>
+    </row>
+    <row r="722" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z722" s="7"/>
+      <c r="AB722" s="7"/>
+    </row>
+    <row r="723" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z723" s="7"/>
+      <c r="AB723" s="7"/>
+    </row>
+    <row r="724" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z724" s="7"/>
+      <c r="AB724" s="7"/>
+    </row>
+    <row r="725" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z725" s="7"/>
+      <c r="AB725" s="7"/>
+    </row>
+    <row r="726" spans="26:28" x14ac:dyDescent="0.25">
+      <c r="Z726" s="7"/>
+      <c r="AB726" s="7"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
